--- a/data/fmsForecastOutput/File1/RPT_RPT3439421614472VV_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT3439421614472VV_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>453.7221316809883</v>
+        <v>224.0381813748386</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>479.6382057339682</v>
+        <v>234.4436520798633</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>510.1929711083108</v>
+        <v>247.3088170229858</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>535.6640358379175</v>
+        <v>257.4997254802472</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>564.1887346997194</v>
+        <v>268.9374258163081</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>449.8786516097338</v>
+        <v>222.1403523763623</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>476.6170797919291</v>
+        <v>232.9669465638546</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>508.0103724101672</v>
+        <v>246.2508323633902</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>534.4487289713954</v>
+        <v>256.9155133486257</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>564.0535731356514</v>
+        <v>268.8729969688233</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>52348635.6763787</v>
+        <v>25848602.57079064</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>59251965.28670226</v>
+        <v>28961903.83823026</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>67234157.14220308</v>
+        <v>32590779.09110129</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>76103389.69077039</v>
+        <v>36583726.63956665</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>88146642.57788362</v>
+        <v>42017701.15047681</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>556.7656797945526</v>
+        <v>274.9165219846886</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>588.5674800158794</v>
+        <v>287.6850411642513</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>626.0614516050148</v>
+        <v>303.4718431246059</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>657.3171776960697</v>
+        <v>315.9770736694263</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>692.320040117364</v>
+        <v>330.0122384640915</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>552.1022247246922</v>
+        <v>272.6138456817593</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>584.9019116785732</v>
+        <v>285.8933670071509</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>623.4133389691096</v>
+        <v>302.1882287642493</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>655.8426985248014</v>
+        <v>315.2682864321576</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>692.1560582115713</v>
+        <v>329.9340728573505</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>52348635.6763787</v>
+        <v>25848602.57079064</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>59251965.28670226</v>
+        <v>28961903.83823026</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>67234157.14220308</v>
+        <v>32590779.09110129</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>76103389.69077039</v>
+        <v>36583726.63956665</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>88146642.57788362</v>
+        <v>42017701.15047681</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>1017.459089724621</v>
+        <v>500.3155164385035</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>1070.108217761866</v>
+        <v>520.2306135590288</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1136.405381929706</v>
+        <v>547.2020723060386</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1186.119106531885</v>
+        <v>565.8818212151383</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1240.56651372168</v>
+        <v>586.6519006132897</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>1008.392970668675</v>
+        <v>495.8574305229347</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>1062.512190779732</v>
+        <v>516.5378227627936</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>1130.486399462452</v>
+        <v>544.3519630725496</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>1182.363996795883</v>
+        <v>564.0903077620884</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>1239.232709843052</v>
+        <v>586.0211576649775</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>26185379.03705674</v>
+        <v>12876145.65378626</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>28339830.28143753</v>
+        <v>13777342.37599495</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>31393998.41144255</v>
+        <v>15116842.33626454</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>35040424.50268856</v>
+        <v>16717325.54052735</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>40019909.31238885</v>
+        <v>18925027.88105373</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>1029.255918687301</v>
+        <v>506.1163752979958</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1082.515481841557</v>
+        <v>526.2623760458793</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1149.581321933861</v>
+        <v>553.5465527084551</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1199.871447407734</v>
+        <v>572.4428821220409</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1254.95013968463</v>
+        <v>593.4537781551566</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>1020.010807239</v>
+        <v>501.5702733903111</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>1074.769372405458</v>
+        <v>522.4966230147837</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>1143.545299376819</v>
+        <v>550.6400863151941</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>1196.042021740731</v>
+        <v>570.6159135160065</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1253.589915892153</v>
+        <v>592.810541485224</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>26185379.03705674</v>
+        <v>12876145.65378626</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>28339830.28143753</v>
+        <v>13777342.37599495</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>31393998.41144255</v>
+        <v>15116842.33626454</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>35040424.50268856</v>
+        <v>16717325.54052735</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>40019909.31238885</v>
+        <v>18925027.88105373</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>556.5366329436075</v>
+        <v>274.4257530261661</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>583.8758171342703</v>
+        <v>284.89459795583</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>618.717075726502</v>
+        <v>299.2810683130813</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>647.6343632879408</v>
+        <v>310.5851238526782</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>679.9449854921439</v>
+        <v>323.3115641626238</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>551.7775802609423</v>
+        <v>272.0790835559537</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>580.1156499506958</v>
+        <v>283.0598721205068</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>615.970359366606</v>
+        <v>297.9524469025717</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>646.0649329909351</v>
+        <v>309.8324738312903</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>679.6847902440752</v>
+        <v>323.1878421176118</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>78534014.71343543</v>
+        <v>38724748.22457689</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>87591795.56813979</v>
+        <v>42739246.21422521</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>98628155.55364563</v>
+        <v>47707621.42736583</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>111143814.193459</v>
+        <v>53301052.180094</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>128166551.8902725</v>
+        <v>60942729.03153054</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>657.3874468596263</v>
+        <v>324.1526670143151</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>690.5087717866628</v>
+        <v>336.9224783781659</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>732.1987916918356</v>
+        <v>354.1711638223279</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>766.6027708011156</v>
+        <v>367.6361367817759</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>805.0142065123338</v>
+        <v>382.7789505756542</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>651.7962579218059</v>
+        <v>321.3957114146916</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>686.0760148143878</v>
+        <v>334.7596000810847</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>728.9500791315085</v>
+        <v>352.5997418263786</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>764.7365933583513</v>
+        <v>366.7411882191144</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>804.6868617059552</v>
+        <v>382.6233012426902</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>78534014.71343543</v>
+        <v>38724748.22457689</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>87591795.56813979</v>
+        <v>42739246.21422521</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>98628155.55364563</v>
+        <v>47707621.42736583</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>111143814.193459</v>
+        <v>53301052.180094</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>128166551.8902725</v>
+        <v>60942729.03153054</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>1179.407969332615</v>
+        <v>579.7402970241324</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>1230.465110090619</v>
+        <v>598.1635061800189</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1289.970159450173</v>
+        <v>621.1549155934647</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1328.432008956238</v>
+        <v>633.8033911196247</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>1362.829974063923</v>
+        <v>644.4859710592705</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>1174.31761983023</v>
+        <v>577.2381257575272</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>1227.323489221914</v>
+        <v>596.636276404463</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>1288.899814624647</v>
+        <v>620.6395161131856</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>1328.432008956238</v>
+        <v>633.8033911196247</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>1362.829974063923</v>
+        <v>644.4859710592705</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>10125003.71617656</v>
+        <v>4976965.405031301</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>11377823.52979895</v>
+        <v>5531078.256075734</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>12953290.64971427</v>
+        <v>6237353.710267489</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>14745983.66859445</v>
+        <v>7035402.934842753</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>17074220.62643371</v>
+        <v>8074444.993085548</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1435.183019264909</v>
+        <v>705.4670237165246</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1497.312785498023</v>
+        <v>727.8856249371488</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1569.722535662487</v>
+        <v>755.8631197795963</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1616.525503537854</v>
+        <v>771.254636342779</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1658.383263281288</v>
+        <v>784.2539188048053</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>1428.530249017573</v>
+        <v>702.1968414729653</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1493.206344253717</v>
+        <v>725.8893689909439</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>1568.323298900815</v>
+        <v>755.1893500910303</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>1616.525503537854</v>
+        <v>771.254636342779</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>1658.383263281288</v>
+        <v>784.2539188048053</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>10125003.71617656</v>
+        <v>4976965.405031301</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>11377823.52979895</v>
+        <v>5531078.256075734</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>12953290.64971427</v>
+        <v>6237353.710267489</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>14745983.66859445</v>
+        <v>7035402.934842753</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>17074220.62643371</v>
+        <v>8074444.993085548</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>592.2570743729767</v>
+        <v>291.9349509456454</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>621.4162343199944</v>
+        <v>303.0827325478266</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>658.4954990427059</v>
+        <v>318.3553079959322</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>688.9940659148612</v>
+        <v>330.2212368976526</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>722.5047206589155</v>
+        <v>343.3282664947804</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>587.3358390529135</v>
+        <v>289.5091774138057</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>617.5540235033444</v>
+        <v>301.1990190348383</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>655.7125690407598</v>
+        <v>317.00987572764</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>687.4256113975231</v>
+        <v>329.4695071949118</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>722.245464133446</v>
+        <v>343.2050698678541</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>88659018.42961198</v>
+        <v>43701713.6296082</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>98969619.09793873</v>
+        <v>48270324.47030095</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>111581446.2033599</v>
+        <v>53944975.13763332</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>125889797.8620534</v>
+        <v>60336455.11493675</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>145240772.5167062</v>
+        <v>69017174.02461608</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>700.7583784623076</v>
+        <v>345.4151498445725</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>736.1076482481225</v>
+        <v>359.0187713795522</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>780.5447491969395</v>
+        <v>377.3586497904277</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>816.9129516635668</v>
+        <v>391.5277226848893</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>856.8473796956793</v>
+        <v>407.1641800468073</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>694.9489660244883</v>
+        <v>342.5516125216632</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>731.5346103227075</v>
+        <v>356.7883950275793</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>777.2407455446719</v>
+        <v>375.7613202492767</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>815.04174792872</v>
+        <v>390.6309026534011</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>856.5201127160568</v>
+        <v>407.0086673869719</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>88659018.42961198</v>
+        <v>43701713.6296082</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>98969619.09793873</v>
+        <v>48270324.47030095</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>111581446.2033599</v>
+        <v>53944975.13763332</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>125889797.8620534</v>
+        <v>60336455.11493675</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>145240772.5167062</v>
+        <v>69017174.02461608</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>6872.00387749361</v>
+        <v>3375.235289087735</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>6995.055024110559</v>
+        <v>3393.266401913837</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>7578.823509603085</v>
+        <v>3618.274729852546</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>7881.862504541635</v>
+        <v>3708.535988983122</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>8375.772568783847</v>
+        <v>3887.384539515085</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>6865.59195168126</v>
+        <v>3372.086024526966</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>6989.183320921446</v>
+        <v>3390.418067900029</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>7573.004354660026</v>
+        <v>3615.49655442032</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>7876.511234683922</v>
+        <v>3706.018135259759</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>8370.75576427064</v>
+        <v>3885.056127641164</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>63801645.87629825</v>
+        <v>31336648.01453846</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>73240741.28708805</v>
+        <v>35528719.33160242</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>88587417.19048609</v>
+        <v>42293320.67135414</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>105584529.871534</v>
+        <v>49679124.53215503</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>128884551.9710699</v>
+        <v>59818221.01783905</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>4406.788946526724</v>
+        <v>2164.426829355</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>4485.697579646819</v>
+        <v>2175.989586028622</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>4860.049014113322</v>
+        <v>2320.279989543122</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>5054.377905229842</v>
+        <v>2378.161551621238</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>5371.106104235856</v>
+        <v>2492.851215602342</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>4403.729224902026</v>
+        <v>2162.924024556492</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>4482.895715291867</v>
+        <v>2174.630415565258</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4857.272275683291</v>
+        <v>2318.954321716175</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>5051.824486632868</v>
+        <v>2376.960129399477</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>5368.712328560663</v>
+        <v>2491.740210441398</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>63801645.87629825</v>
+        <v>31336648.01453846</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>73240741.28708805</v>
+        <v>35528719.33160242</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>88587417.19048609</v>
+        <v>42293320.67135414</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>105584529.871534</v>
+        <v>49679124.53215503</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>128884551.9710699</v>
+        <v>59818221.01783905</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>958.9858811120989</v>
+        <v>471.9956753998874</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>1014.583811687452</v>
+        <v>493.705515194162</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>1105.063563720705</v>
+        <v>531.298898944108</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>1180.321548624749</v>
+        <v>560.985894375352</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>1266.684061122962</v>
+        <v>595.325618665974</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>951.4276121432524</v>
+        <v>468.2756284799286</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>1008.612744924756</v>
+        <v>490.7999392025544</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>1100.63916720926</v>
+        <v>529.1717105631626</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>1177.763222935064</v>
+        <v>559.7699668710385</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>1266.207903565939</v>
+        <v>595.1018304681496</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>152460664.3059102</v>
+        <v>75038361.64414667</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>172210360.3850268</v>
+        <v>83799043.80190337</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>200168863.393846</v>
+        <v>96238295.80898745</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>231474327.7335874</v>
+        <v>110015579.6470918</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>274125324.4877761</v>
+        <v>128835395.0424552</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>1081.306569428359</v>
+        <v>532.1966847708869</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>1142.148620365881</v>
+        <v>555.7765056506262</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>1241.888875654882</v>
+        <v>597.0791594842848</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>1322.755665230156</v>
+        <v>628.6787379750886</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>1416.654391590981</v>
+        <v>665.8060384967744</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>1073.179973465848</v>
+        <v>528.1969628720509</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>1135.740740296837</v>
+        <v>552.6584078812191</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>1237.144602878225</v>
+        <v>594.798205043566</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>1320.007262665877</v>
+        <v>627.3724850538082</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>1416.102113032221</v>
+        <v>665.5464772905086</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>152460664.3059102</v>
+        <v>75038361.64414667</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>172210360.3850268</v>
+        <v>83799043.80190337</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>200168863.393846</v>
+        <v>96238295.80898745</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>231474327.7335874</v>
+        <v>110015579.6470918</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>274125324.4877761</v>
+        <v>128835395.0424552</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3152,22 +3152,22 @@
         </is>
       </c>
       <c r="C19" s="74" t="n">
-        <v>115375.9801895337</v>
+        <v>115375.8810760176</v>
       </c>
       <c r="D19" s="75" t="n">
-        <v>123534.7071570992</v>
+        <v>123534.6045043027</v>
       </c>
       <c r="E19" s="75" t="n">
-        <v>131781.8177623025</v>
+        <v>131781.7111553778</v>
       </c>
       <c r="F19" s="75" t="n">
-        <v>142072.9871695138</v>
+        <v>142072.8762771943</v>
       </c>
       <c r="G19" s="76" t="n">
-        <v>156236.0911456311</v>
+        <v>156235.9757960058</v>
       </c>
       <c r="H19" s="74" t="n">
-        <v>985.6997636433864</v>
+        <v>985.6997636334097</v>
       </c>
       <c r="I19" s="75" t="n">
         <v>783.0477008869115</v>
@@ -3182,19 +3182,19 @@
         <v>37.4381361076853</v>
       </c>
       <c r="M19" s="74" t="n">
-        <v>116361.6799531771</v>
+        <v>116361.580839651</v>
       </c>
       <c r="N19" s="75" t="n">
-        <v>124317.7548579861</v>
+        <v>124317.6522051896</v>
       </c>
       <c r="O19" s="75" t="n">
-        <v>132348.0007371154</v>
+        <v>132347.8941301906</v>
       </c>
       <c r="P19" s="75" t="n">
-        <v>142396.0532888527</v>
+        <v>142395.9423965332</v>
       </c>
       <c r="Q19" s="76" t="n">
-        <v>156273.5292817388</v>
+        <v>156273.4139321135</v>
       </c>
       <c r="S19" s="21" t="inlineStr">
         <is>
@@ -3202,22 +3202,22 @@
         </is>
       </c>
       <c r="T19" s="74" t="n">
-        <v>94022.74165982254</v>
+        <v>94023.45986404654</v>
       </c>
       <c r="U19" s="75" t="n">
-        <v>100671.4901834258</v>
+        <v>100672.262002301</v>
       </c>
       <c r="V19" s="75" t="n">
-        <v>107392.2647207186</v>
+        <v>107393.0904282263</v>
       </c>
       <c r="W19" s="75" t="n">
-        <v>115778.7933635276</v>
+        <v>115779.6868447499</v>
       </c>
       <c r="X19" s="76" t="n">
-        <v>127320.6573118131</v>
+        <v>127321.6452396772</v>
       </c>
       <c r="Y19" s="74" t="n">
-        <v>794.1841413414386</v>
+        <v>794.1841413334002</v>
       </c>
       <c r="Z19" s="75" t="n">
         <v>630.9061733560982</v>
@@ -3232,19 +3232,19 @@
         <v>30.16412813999912</v>
       </c>
       <c r="AD19" s="74" t="n">
-        <v>94816.92580116398</v>
+        <v>94817.64400537995</v>
       </c>
       <c r="AE19" s="75" t="n">
-        <v>101302.3963567819</v>
+        <v>101303.1681756571</v>
       </c>
       <c r="AF19" s="75" t="n">
-        <v>107848.4416990227</v>
+        <v>107849.2674065304</v>
       </c>
       <c r="AG19" s="75" t="n">
-        <v>116039.0896505383</v>
+        <v>116039.9831317606</v>
       </c>
       <c r="AH19" s="76" t="n">
-        <v>127350.8214399531</v>
+        <v>127351.8093678172</v>
       </c>
       <c r="AR19" s="77" t="inlineStr">
         <is>
@@ -3409,22 +3409,22 @@
         </is>
       </c>
       <c r="C21" s="85" t="n">
-        <v>141112.0312027925</v>
+        <v>141111.9320892764</v>
       </c>
       <c r="D21" s="86" t="n">
-        <v>150017.8513952683</v>
+        <v>150017.7487424717</v>
       </c>
       <c r="E21" s="86" t="n">
-        <v>159407.5215038081</v>
+        <v>159407.4148968833</v>
       </c>
       <c r="F21" s="86" t="n">
-        <v>171615.0662994452</v>
+        <v>171614.9554071258</v>
       </c>
       <c r="G21" s="87" t="n">
-        <v>188495.4733470173</v>
+        <v>188495.357997392</v>
       </c>
       <c r="H21" s="85" t="n">
-        <v>1217.083866173766</v>
+        <v>1217.083866163789</v>
       </c>
       <c r="I21" s="86" t="n">
         <v>972.3788727554111</v>
@@ -3439,19 +3439,19 @@
         <v>72.15937027183648</v>
       </c>
       <c r="M21" s="85" t="n">
-        <v>142329.1150689663</v>
+        <v>142329.0159554402</v>
       </c>
       <c r="N21" s="86" t="n">
-        <v>150990.2302680237</v>
+        <v>150990.1276152272</v>
       </c>
       <c r="O21" s="86" t="n">
-        <v>160118.3466929539</v>
+        <v>160118.2400860292</v>
       </c>
       <c r="P21" s="86" t="n">
-        <v>172031.9561052827</v>
+        <v>172031.8452129632</v>
       </c>
       <c r="Q21" s="87" t="n">
-        <v>188567.6327172891</v>
+        <v>188567.5173676638</v>
       </c>
       <c r="S21" s="42" t="inlineStr">
         <is>
@@ -3459,22 +3459,22 @@
         </is>
       </c>
       <c r="T21" s="85" t="n">
-        <v>119463.8186180714</v>
+        <v>119464.5368222954</v>
       </c>
       <c r="U21" s="86" t="n">
-        <v>126851.0975486954</v>
+        <v>126851.8693675706</v>
       </c>
       <c r="V21" s="86" t="n">
-        <v>134701.3361299779</v>
+        <v>134702.1618374856</v>
       </c>
       <c r="W21" s="86" t="n">
-        <v>144982.2756018889</v>
+        <v>144983.1690831112</v>
       </c>
       <c r="X21" s="87" t="n">
-        <v>159210.2982201331</v>
+        <v>159211.2861479972</v>
       </c>
       <c r="Y21" s="85" t="n">
-        <v>1024.775415644186</v>
+        <v>1024.775415636147</v>
       </c>
       <c r="Z21" s="86" t="n">
         <v>819.5886096555309</v>
@@ -3489,19 +3489,19 @@
         <v>64.76639140579327</v>
       </c>
       <c r="AD21" s="85" t="n">
-        <v>120488.5940337156</v>
+        <v>120489.3122379315</v>
       </c>
       <c r="AE21" s="86" t="n">
-        <v>127670.6861583509</v>
+        <v>127671.4579772261</v>
       </c>
       <c r="AF21" s="86" t="n">
-        <v>135301.6597119434</v>
+        <v>135302.4854194511</v>
       </c>
       <c r="AG21" s="86" t="n">
-        <v>145336.0740923478</v>
+        <v>145336.9675735701</v>
       </c>
       <c r="AH21" s="87" t="n">
-        <v>159275.0646115389</v>
+        <v>159276.052539403</v>
       </c>
       <c r="AR21" s="20" t="inlineStr">
         <is>
@@ -3703,22 +3703,22 @@
         </is>
       </c>
       <c r="C23" s="85" t="n">
-        <v>149696.8500097283</v>
+        <v>149696.7508962122</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>159264.6178712077</v>
+        <v>159264.5152184111</v>
       </c>
       <c r="E23" s="86" t="n">
-        <v>169449.0643680519</v>
+        <v>169448.9577611271</v>
       </c>
       <c r="F23" s="86" t="n">
-        <v>182715.3586510128</v>
+        <v>182715.2477586933</v>
       </c>
       <c r="G23" s="87" t="n">
-        <v>201023.9772333229</v>
+        <v>201023.8618836977</v>
       </c>
       <c r="H23" s="85" t="n">
-        <v>1254.296735506568</v>
+        <v>1254.296735496591</v>
       </c>
       <c r="I23" s="86" t="n">
         <v>996.0481292993957</v>
@@ -3733,19 +3733,19 @@
         <v>72.15937027183648</v>
       </c>
       <c r="M23" s="85" t="n">
-        <v>150951.1467452348</v>
+        <v>150951.0476317088</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>160260.666000507</v>
+        <v>160260.5633477105</v>
       </c>
       <c r="O23" s="86" t="n">
-        <v>170168.2283848731</v>
+        <v>170168.1217779483</v>
       </c>
       <c r="P23" s="86" t="n">
-        <v>183132.2484568503</v>
+        <v>183132.1375645308</v>
       </c>
       <c r="Q23" s="87" t="n">
-        <v>201096.1366035948</v>
+        <v>201096.0212539695</v>
       </c>
       <c r="S23" s="42" t="inlineStr">
         <is>
@@ -3753,22 +3753,22 @@
         </is>
       </c>
       <c r="T23" s="85" t="n">
-        <v>126518.6705639664</v>
+        <v>126519.3887681904</v>
       </c>
       <c r="U23" s="86" t="n">
-        <v>134449.9263572095</v>
+        <v>134450.6981760847</v>
       </c>
       <c r="V23" s="86" t="n">
-        <v>142953.2980884953</v>
+        <v>142954.123796003</v>
       </c>
       <c r="W23" s="86" t="n">
-        <v>154104.2991247606</v>
+        <v>154105.192605983</v>
       </c>
       <c r="X23" s="87" t="n">
-        <v>169506.0006699097</v>
+        <v>169506.9885977738</v>
       </c>
       <c r="Y23" s="85" t="n">
-        <v>1057.63037909861</v>
+        <v>1057.630379090571</v>
       </c>
       <c r="Z23" s="86" t="n">
         <v>840.4860188768221</v>
@@ -3783,19 +3783,19 @@
         <v>64.76639140579327</v>
       </c>
       <c r="AD23" s="85" t="n">
-        <v>127576.300943065</v>
+        <v>127577.019147281</v>
       </c>
       <c r="AE23" s="86" t="n">
-        <v>135290.4123760863</v>
+        <v>135291.1841949616</v>
       </c>
       <c r="AF23" s="86" t="n">
-        <v>143560.9839589229</v>
+        <v>143561.8096664305</v>
       </c>
       <c r="AG23" s="86" t="n">
-        <v>154458.0976152196</v>
+        <v>154458.9910964419</v>
       </c>
       <c r="AH23" s="87" t="n">
-        <v>169570.7670613155</v>
+        <v>169571.7549891796</v>
       </c>
       <c r="AR23" s="90" t="inlineStr">
         <is>
@@ -3942,22 +3942,22 @@
         </is>
       </c>
       <c r="C25" s="91" t="n">
-        <v>158981.1354981655</v>
+        <v>158981.0363846494</v>
       </c>
       <c r="D25" s="92" t="n">
-        <v>169734.9774373071</v>
+        <v>169734.8747845106</v>
       </c>
       <c r="E25" s="92" t="n">
-        <v>181137.8729381732</v>
+        <v>181137.7663312485</v>
       </c>
       <c r="F25" s="92" t="n">
-        <v>196111.2444344421</v>
+        <v>196111.1335421227</v>
       </c>
       <c r="G25" s="93" t="n">
-        <v>216411.7579917711</v>
+        <v>216411.6426421458</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>1262.967531876568</v>
+        <v>1262.967531866591</v>
       </c>
       <c r="I25" s="92" t="n">
         <v>1004.844413619396</v>
@@ -3972,19 +3972,19 @@
         <v>81.38165439183648</v>
       </c>
       <c r="M25" s="91" t="n">
-        <v>160244.1030300421</v>
+        <v>160244.003916516</v>
       </c>
       <c r="N25" s="92" t="n">
-        <v>170739.8218509265</v>
+        <v>170739.7191981299</v>
       </c>
       <c r="O25" s="92" t="n">
-        <v>181866.0187256345</v>
+        <v>181865.9121187098</v>
       </c>
       <c r="P25" s="92" t="n">
-        <v>196537.2353508696</v>
+        <v>196537.1244585501</v>
       </c>
       <c r="Q25" s="93" t="n">
-        <v>216493.1396461629</v>
+        <v>216493.0242965377</v>
       </c>
       <c r="S25" s="51" t="inlineStr">
         <is>
@@ -3992,22 +3992,22 @@
         </is>
       </c>
       <c r="T25" s="91" t="n">
-        <v>140996.7058523558</v>
+        <v>140997.4240565798</v>
       </c>
       <c r="U25" s="92" t="n">
-        <v>150777.5409559749</v>
+        <v>150778.3127748501</v>
       </c>
       <c r="V25" s="92" t="n">
-        <v>161180.9778779857</v>
+        <v>161181.8035854934</v>
       </c>
       <c r="W25" s="92" t="n">
-        <v>174994.0172762831</v>
+        <v>174994.9107575055</v>
       </c>
       <c r="X25" s="93" t="n">
-        <v>193501.9056976333</v>
+        <v>193502.8936254974</v>
       </c>
       <c r="Y25" s="91" t="n">
-        <v>1067.689752732331</v>
+        <v>1067.689752724293</v>
       </c>
       <c r="Z25" s="92" t="n">
         <v>850.6909766208969</v>
@@ -4022,19 +4022,19 @@
         <v>75.4655703232448</v>
       </c>
       <c r="AD25" s="91" t="n">
-        <v>142064.3956050882</v>
+        <v>142065.1138093041</v>
       </c>
       <c r="AE25" s="92" t="n">
-        <v>151628.2319325958</v>
+        <v>151629.003751471</v>
       </c>
       <c r="AF25" s="92" t="n">
-        <v>161799.0838970253</v>
+        <v>161799.909604533</v>
       </c>
       <c r="AG25" s="92" t="n">
-        <v>175358.3743668982</v>
+        <v>175359.2678481206</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>193577.3712679565</v>
+        <v>193578.3591958206</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>466.5139043792844</v>
+        <v>460.7066282194476</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>504.7577556741168</v>
+        <v>493.4391394214569</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>540.3376300767244</v>
+        <v>523.8349286262353</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>574.5108152936256</v>
+        <v>552.3384084302189</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>606.6256786235655</v>
+        <v>578.3203580219408</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>462.5620652044972</v>
+        <v>456.8039791555264</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>501.5784077158387</v>
+        <v>490.3310821440089</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>538.0260729311967</v>
+        <v>521.5939680114125</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>573.2073734121385</v>
+        <v>551.0852700108919</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>606.4803505259208</v>
+        <v>578.1818108709399</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>53824498.98980633</v>
+        <v>53154433.14838003</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>62355101.53247666</v>
+        <v>60956808.93537315</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>71206675.09688532</v>
+        <v>69031863.25732046</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>81622467.68995816</v>
+        <v>78472306.36404891</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>94776824.81671168</v>
+        <v>90354445.45825335</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>572.4625557564061</v>
+        <v>565.3316015517704</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>619.3918597893426</v>
+        <v>605.4975593374459</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>663.0521786840372</v>
+        <v>642.7961331781987</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>704.9863391966451</v>
+        <v>677.7726603222995</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>744.3947181689429</v>
+        <v>709.6550259633012</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>567.6676240556365</v>
+        <v>560.596434407968</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>615.5343187822049</v>
+        <v>601.7265800579464</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>660.2476027943443</v>
+        <v>640.077257058313</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>703.4049296299311</v>
+        <v>676.2523075769968</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>744.2184019315469</v>
+        <v>709.48693942221</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>53824498.98980633</v>
+        <v>53154433.14838003</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>62355101.53247666</v>
+        <v>60956808.93537315</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>71206675.09688532</v>
+        <v>69031863.25732046</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>81622467.68995816</v>
+        <v>78472306.36404891</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>94776824.81671168</v>
+        <v>90354445.45825335</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,49 +4510,49 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>1046.50330028198</v>
+        <v>1029.194438011743</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>1126.54800055247</v>
+        <v>1095.336631810123</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1203.99147039808</v>
+        <v>1159.491296192618</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>1272.60734872956</v>
+        <v>1214.287273673856</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1334.38924056399</v>
+        <v>1262.03819770399</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>1037.178381365225</v>
+        <v>1020.023750560066</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>1118.551342955761</v>
+        <v>1087.561524141898</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>1197.720464894825</v>
+        <v>1153.452070435482</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>1268.578427671797</v>
+        <v>1210.442986925109</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>1332.954562515714</v>
+        <v>1260.681308392168</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>26932862.32160074</v>
+        <v>26487400.55923246</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>29834533.18985203</v>
+        <v>29007958.00957777</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>33261111.66851704</v>
+        <v>32031763.03947157</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>37595466.99750097</v>
+        <v>35872570.7253418</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>43046572.51677119</v>
+        <v>40712572.57248159</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,49 +4560,49 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1058.636879476449</v>
+        <v>1041.127331311514</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1139.60965012146</v>
+        <v>1108.036404245709</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1217.951030632247</v>
+        <v>1172.934903550436</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1287.362468990637</v>
+        <v>1228.366207582606</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1349.860684870251</v>
+        <v>1276.670774986987</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>1049.127858681578</v>
+        <v>1031.775586973601</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>1131.454994403042</v>
+        <v>1100.107675843722</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>1211.556024246877</v>
+        <v>1166.776260050677</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>1283.253813107426</v>
+        <v>1224.445840034934</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1348.397588798123</v>
+        <v>1275.287008486324</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>26932862.32160074</v>
+        <v>26487400.55923246</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>29834533.18985203</v>
+        <v>29007958.00957777</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>33261111.66851704</v>
+        <v>32031763.03947157</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>37595466.99750097</v>
+        <v>35872570.7253418</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>43046572.51677119</v>
+        <v>40712572.57248159</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>572.2925297230711</v>
+        <v>564.3876639519469</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>614.524430692096</v>
+        <v>599.694154185643</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>655.3504237433785</v>
+        <v>633.9957671490223</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>694.6822167666786</v>
+        <v>666.287368825916</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>731.1761650623414</v>
+        <v>695.3328687942987</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>567.398745311356</v>
+        <v>559.5614722197365</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>610.5668860739022</v>
+        <v>595.8321140982868</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>652.4410782590196</v>
+        <v>631.1812210931873</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>692.9987741027506</v>
+        <v>664.6727351429607</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>730.8963651260088</v>
+        <v>695.066784886307</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>80757361.31140707</v>
+        <v>79641833.70761248</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>92189634.72232869</v>
+        <v>89964766.94495091</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>104467786.7654024</v>
+        <v>101063626.296792</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>119217934.6874591</v>
+        <v>114344877.0893907</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>137823397.3334829</v>
+        <v>131067018.0307349</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>675.9984926447919</v>
+        <v>666.6566985153131</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>726.7547266348178</v>
+        <v>709.2112035358797</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>775.5512288653011</v>
+        <v>750.2747165908331</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>822.2931678546914</v>
+        <v>788.6769051367808</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>865.6688598304144</v>
+        <v>823.2269282021858</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>670.2490136851397</v>
+        <v>660.9867068569777</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>722.0892868703252</v>
+        <v>704.6584128537072</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>772.1101647076152</v>
+        <v>746.9458227872516</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>820.2914206400472</v>
+        <v>786.7570033860031</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>865.3168508807377</v>
+        <v>822.8921795905918</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>80757361.31140707</v>
+        <v>79641833.70761248</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>92189634.72232869</v>
+        <v>89964766.94495091</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>104467786.7654024</v>
+        <v>101063626.296792</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>119217934.6874591</v>
+        <v>114344877.0893907</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>137823397.3334829</v>
+        <v>131067018.0307349</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,49 +4714,49 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>1212.942720733083</v>
+        <v>1192.445851264407</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>1295.223969473462</v>
+        <v>1259.284161266991</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>1366.544511769841</v>
+        <v>1316.047905054163</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1425.147809083238</v>
+        <v>1359.885058509356</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1465.747624492743</v>
+        <v>1386.300910065538</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>1207.707634541153</v>
+        <v>1187.299229990482</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>1291.917006424469</v>
+        <v>1256.068959658898</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>1365.410629845278</v>
+        <v>1314.955922379215</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>1425.147809083238</v>
+        <v>1359.885058509356</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>1465.747624492743</v>
+        <v>1386.300910065538</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>10412893.48068521</v>
+        <v>10236931.57018722</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>11976633.57976029</v>
+        <v>11644306.56608501</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>13722215.29083391</v>
+        <v>13215151.44999958</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>15819557.32501994</v>
+        <v>15095121.71398241</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>18363624.80980063</v>
+        <v>17368276.33934517</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1475.990362454608</v>
+        <v>1451.04839175877</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1576.115725405078</v>
+        <v>1532.381747176364</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1662.9033628385</v>
+        <v>1601.455692165351</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1734.215800403861</v>
+        <v>1654.799691771698</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1783.620389126441</v>
+        <v>1686.944278359754</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>1469.148430354741</v>
+        <v>1444.322077805389</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>1571.793163891353</v>
+        <v>1528.179127877596</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>1661.421065512998</v>
+        <v>1600.028168749104</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>1734.215800403861</v>
+        <v>1654.799691771698</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1783.620389126441</v>
+        <v>1686.944278359754</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>10412893.48068521</v>
+        <v>10236931.57018722</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>11976633.57976029</v>
+        <v>11644306.56608501</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>13722215.29083391</v>
+        <v>13215151.44999958</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>15819557.32501994</v>
+        <v>15095121.71398241</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>18363624.80980063</v>
+        <v>17368276.33934517</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>609.0325533647999</v>
+        <v>600.405584888843</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>654.0452593577627</v>
+        <v>637.9894063137162</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>697.4957489261886</v>
+        <v>674.4141672909602</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>739.0593380297128</v>
+        <v>708.4247231206491</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>776.9571784066416</v>
+        <v>738.396392245003</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>603.9719257380885</v>
+        <v>595.4166379625694</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>649.9802534313656</v>
+        <v>634.0241877883524</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>694.5479962859073</v>
+        <v>671.5639601165341</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>737.3769128613997</v>
+        <v>706.8120348770678</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>776.6783826939594</v>
+        <v>738.1314331555931</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>91170254.79209229</v>
+        <v>89878765.27779971</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>104166268.302089</v>
+        <v>101609073.5110359</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>118190002.0562363</v>
+        <v>114278777.7467916</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>135037492.0124791</v>
+        <v>129439998.8033731</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>156187022.1432835</v>
+        <v>148435294.3700801</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>720.607119768917</v>
+        <v>710.3951904358006</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>774.758834938576</v>
+        <v>755.7348149874429</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>826.7735241971872</v>
+        <v>799.4087523481913</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>876.2733601815653</v>
+        <v>839.9457319671639</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>921.4247373309036</v>
+        <v>875.6883453478423</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>714.6331577114775</v>
+        <v>704.5059202554294</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>769.9456781351432</v>
+        <v>751.0398708951502</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>823.2738366439032</v>
+        <v>796.0249178546942</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>874.2661867355092</v>
+        <v>838.0217809564269</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>921.0728054724638</v>
+        <v>875.3538841392058</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>91170254.79209229</v>
+        <v>89878765.27779971</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>104166268.302089</v>
+        <v>101609073.5110359</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>118190002.0562363</v>
+        <v>114278777.7467916</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>135037492.0124791</v>
+        <v>129439998.8033731</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>156187022.1432835</v>
+        <v>148435294.3700801</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>7068.508411328544</v>
+        <v>6942.066310565273</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>7363.990971797621</v>
+        <v>7142.221825372108</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>8030.116030518208</v>
+        <v>7665.143286208037</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>8456.934017748536</v>
+        <v>7955.939721301902</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>9009.113228766104</v>
+        <v>8360.618382294664</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>7061.913136886711</v>
+        <v>6935.589012973294</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>7357.809580925831</v>
+        <v>7136.226589233886</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>8023.95036518333</v>
+        <v>7659.257853411421</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>8451.192311892621</v>
+        <v>7950.538157852165</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>9003.717074616156</v>
+        <v>8355.610654626673</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>65626050.06819405</v>
+        <v>64452125.5069501</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>77103633.31623124</v>
+        <v>74781630.61248915</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>93862489.07659048</v>
+        <v>89596392.53503703</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>113288122.1797575</v>
+        <v>106576859.8064089</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>138630259.1922878</v>
+        <v>128651362.6718017</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>4532.800809017408</v>
+        <v>4451.717669084369</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>4722.284008471227</v>
+        <v>4580.070784996583</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>5149.447991219879</v>
+        <v>4915.403033725444</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>5423.152258830303</v>
+        <v>5101.881175866481</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>5777.246535695231</v>
+        <v>5361.388225331151</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>4529.653594838537</v>
+        <v>4448.626752549806</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4719.334367082712</v>
+        <v>4577.209973083212</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>5146.505907695795</v>
+        <v>4912.594669352328</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>5420.412539305653</v>
+        <v>5099.303759116434</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>5774.671752781181</v>
+        <v>5358.998780686046</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>65626050.06819405</v>
+        <v>64452125.5069501</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>77103633.31623124</v>
+        <v>74781630.61248915</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>93862489.07659048</v>
+        <v>89596392.53503703</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>113288122.1797575</v>
+        <v>106576859.8064089</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>138630259.1922878</v>
+        <v>128651362.6718017</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>986.2572963073069</v>
+        <v>970.7503127061726</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>1067.958439416376</v>
+        <v>1039.213092462374</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>1170.668992040143</v>
+        <v>1125.525473848452</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1266.248729940874</v>
+        <v>1203.485260356664</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>1362.297890241165</v>
+        <v>1280.368531281227</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>978.4840870611673</v>
+        <v>963.0993173707342</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>1061.673250289482</v>
+        <v>1033.097072854136</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>1165.981927897877</v>
+        <v>1121.019150354865</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>1263.504158633917</v>
+        <v>1200.876726267348</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>1361.785790614066</v>
+        <v>1279.887229356393</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>156796304.8602863</v>
+        <v>154330890.7847498</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>181269901.6183202</v>
+        <v>176390704.1235251</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>212052491.1328268</v>
+        <v>203875170.2818286</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>248325614.1922365</v>
+        <v>236016858.609782</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>294817281.3355713</v>
+        <v>277086657.0418819</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>1112.056511621449</v>
+        <v>1094.565321440337</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>1202.23410243339</v>
+        <v>1169.867873418379</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>1315.617350909429</v>
+        <v>1264.877087528618</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>1419.052022791021</v>
+        <v>1348.706985752495</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1523.588515951123</v>
+        <v>1431.950974222387</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>1103.698813432115</v>
+        <v>1086.339120467747</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>1195.489120382946</v>
+        <v>1163.304511402317</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>1310.591420083593</v>
+        <v>1260.045019679769</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>1416.103537049623</v>
+        <v>1345.904676188527</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>1522.994549437677</v>
+        <v>1431.392735184751</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>156796304.8602863</v>
+        <v>154330890.7847498</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>181269901.6183202</v>
+        <v>176390704.1235251</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>212052491.1328268</v>
+        <v>203875170.2818286</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>248325614.1922365</v>
+        <v>236016858.609782</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>294817281.3355713</v>
+        <v>277086657.0418819</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5371,34 +5371,34 @@
         </is>
       </c>
       <c r="C46" s="148" t="n">
-        <v>0.1586385501097769</v>
+        <v>0.1586386863880384</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.1749302328304136</v>
+        <v>0.1749303781911219</v>
       </c>
       <c r="E46" s="149" t="n">
-        <v>0.1943657082330656</v>
+        <v>0.1943658654683166</v>
       </c>
       <c r="F46" s="149" t="n">
-        <v>0.214196381733541</v>
+        <v>0.2141965489205102</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2323322653354023</v>
+        <v>0.2323324368672126</v>
       </c>
       <c r="H46" s="148" t="n">
-        <v>0.1572947229889338</v>
+        <v>0.1572948569681606</v>
       </c>
       <c r="I46" s="149" t="n">
-        <v>0.1738283892780591</v>
+        <v>0.1738285328133492</v>
       </c>
       <c r="J46" s="149" t="n">
-        <v>0.1935342143360962</v>
+        <v>0.1935343702289237</v>
       </c>
       <c r="K46" s="149" t="n">
-        <v>0.2137104160608638</v>
+        <v>0.2137105824900705</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.2322766059603833</v>
+        <v>0.2322767774100163</v>
       </c>
       <c r="M46" s="151" t="n">
         <v>18303.07821476196</v>
@@ -5413,7 +5413,7 @@
         <v>30431.51979378564</v>
       </c>
       <c r="Q46" s="153" t="n">
-        <v>36298.68498301286</v>
+        <v>36298.68498301287</v>
       </c>
       <c r="S46" s="21" t="inlineStr">
         <is>
@@ -5421,34 +5421,34 @@
         </is>
       </c>
       <c r="T46" s="148" t="n">
-        <v>0.1946665018659328</v>
+        <v>0.1946650148933824</v>
       </c>
       <c r="U46" s="149" t="n">
-        <v>0.2146581425014619</v>
+        <v>0.2146564967928744</v>
       </c>
       <c r="V46" s="149" t="n">
-        <v>0.2385075536699169</v>
+        <v>0.2385057198696517</v>
       </c>
       <c r="W46" s="149" t="n">
-        <v>0.2628419152567547</v>
+        <v>0.2628398868844026</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.2850965880117631</v>
+        <v>0.285094375859519</v>
       </c>
       <c r="Y46" s="148" t="n">
-        <v>0.1930359802335763</v>
+        <v>0.1930345180663152</v>
       </c>
       <c r="Z46" s="149" t="n">
-        <v>0.2133212625051748</v>
+        <v>0.2133196372314558</v>
       </c>
       <c r="AA46" s="149" t="n">
-        <v>0.2374987152164186</v>
+        <v>0.2374968968964899</v>
       </c>
       <c r="AB46" s="149" t="n">
-        <v>0.2622523141592439</v>
+        <v>0.2622502948766493</v>
       </c>
       <c r="AC46" s="150" t="n">
-        <v>0.2850290604535124</v>
+        <v>0.2850268493490744</v>
       </c>
       <c r="AD46" s="151" t="n">
         <v>18303.07821476196</v>
@@ -5463,7 +5463,7 @@
         <v>30431.51979378564</v>
       </c>
       <c r="AH46" s="153" t="n">
-        <v>36298.68498301286</v>
+        <v>36298.68498301287</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" thickBot="1">
@@ -5575,37 +5575,37 @@
         </is>
       </c>
       <c r="C48" s="161" t="n">
-        <v>0.1344987440739917</v>
+        <v>0.1344988385425688</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.1487184323857965</v>
+        <v>0.1487185341495086</v>
       </c>
       <c r="E48" s="162" t="n">
-        <v>0.1652451100048923</v>
+        <v>0.1652452205158935</v>
       </c>
       <c r="F48" s="162" t="n">
-        <v>0.1817335160110373</v>
+        <v>0.1817336334416602</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.1967463162252991</v>
+        <v>0.1967464366240935</v>
       </c>
       <c r="H48" s="161" t="n">
-        <v>0.1333486192288132</v>
+        <v>0.1333487120886687</v>
       </c>
       <c r="I48" s="162" t="n">
-        <v>0.1477606839183324</v>
+        <v>0.1477607843755455</v>
       </c>
       <c r="J48" s="162" t="n">
-        <v>0.1645115251971508</v>
+        <v>0.1645116347291302</v>
       </c>
       <c r="K48" s="162" t="n">
-        <v>0.1812931161462724</v>
+        <v>0.181293233008439</v>
       </c>
       <c r="L48" s="163" t="n">
-        <v>0.1966710271097836</v>
+        <v>0.1966711474164494</v>
       </c>
       <c r="M48" s="164" t="n">
-        <v>18979.39097050553</v>
+        <v>18979.39097050552</v>
       </c>
       <c r="N48" s="165" t="n">
         <v>22310.41968938968</v>
@@ -5614,10 +5614,10 @@
         <v>26341.31342650401</v>
       </c>
       <c r="P48" s="165" t="n">
-        <v>31188.20939906546</v>
+        <v>31188.20939906545</v>
       </c>
       <c r="Q48" s="166" t="n">
-        <v>37085.79000616969</v>
+        <v>37085.7900061697</v>
       </c>
       <c r="S48" s="42" t="inlineStr">
         <is>
@@ -5625,37 +5625,37 @@
         </is>
       </c>
       <c r="T48" s="161" t="n">
-        <v>0.1588714574006971</v>
+        <v>0.1588705022875328</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.175878806888724</v>
+        <v>0.175877736769824</v>
       </c>
       <c r="V48" s="162" t="n">
-        <v>0.1955534680152421</v>
+        <v>0.1955522692967918</v>
       </c>
       <c r="W48" s="162" t="n">
-        <v>0.2151173946579931</v>
+        <v>0.2151160689637492</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.232935874254144</v>
+        <v>0.2329344288551005</v>
       </c>
       <c r="Y48" s="161" t="n">
-        <v>0.1575202293853196</v>
+        <v>0.1575192904498178</v>
       </c>
       <c r="Z48" s="162" t="n">
-        <v>0.1747497437408451</v>
+        <v>0.1747486873171715</v>
       </c>
       <c r="AA48" s="162" t="n">
-        <v>0.1946858115605125</v>
+        <v>0.194684623455684</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.2145937241929915</v>
+        <v>0.2145924049452722</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.2328411549957265</v>
+        <v>0.2328397107719324</v>
       </c>
       <c r="AD48" s="164" t="n">
-        <v>18979.39097050553</v>
+        <v>18979.39097050552</v>
       </c>
       <c r="AE48" s="165" t="n">
         <v>22310.41968938968</v>
@@ -5664,10 +5664,10 @@
         <v>26341.31342650401</v>
       </c>
       <c r="AG48" s="165" t="n">
-        <v>31188.20939906546</v>
+        <v>31188.20939906545</v>
       </c>
       <c r="AH48" s="166" t="n">
-        <v>37085.79000616969</v>
+        <v>37085.7900061697</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" thickBot="1">
@@ -5742,7 +5742,7 @@
         <v>0.1888412105085668</v>
       </c>
       <c r="Y49" s="155" t="n">
-        <v>0.1870148677191931</v>
+        <v>0.187014867719193</v>
       </c>
       <c r="Z49" s="156" t="n">
         <v>0.1896093637350641</v>
@@ -5779,37 +5779,37 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>0.1356401122620174</v>
+        <v>0.135640202068699</v>
       </c>
       <c r="D50" s="162" t="n">
-        <v>0.1491554837910073</v>
+        <v>0.1491555799281004</v>
       </c>
       <c r="E50" s="162" t="n">
-        <v>0.1648148442278476</v>
+        <v>0.1648149479192715</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.1802779008783003</v>
+        <v>0.1802780102913615</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.1941561571758201</v>
+        <v>0.1941562685846836</v>
       </c>
       <c r="H50" s="161" t="n">
-        <v>0.134513039340199</v>
+        <v>0.1345131276606303</v>
       </c>
       <c r="I50" s="162" t="n">
-        <v>0.1482284563156298</v>
+        <v>0.1482285512614183</v>
       </c>
       <c r="J50" s="162" t="n">
-        <v>0.164118304653265</v>
+        <v>0.1641184074701004</v>
       </c>
       <c r="K50" s="162" t="n">
-        <v>0.1798675088270519</v>
+        <v>0.1798676177425351</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.1940864880798701</v>
+        <v>0.1940865994087942</v>
       </c>
       <c r="M50" s="164" t="n">
-        <v>20304.89754058993</v>
+        <v>20304.89754058992</v>
       </c>
       <c r="N50" s="165" t="n">
         <v>23755.19112936988</v>
@@ -5821,7 +5821,7 @@
         <v>32939.54131583038</v>
       </c>
       <c r="Q50" s="166" t="n">
-        <v>39030.04291982152</v>
+        <v>39030.04291982154</v>
       </c>
       <c r="S50" s="42" t="inlineStr">
         <is>
@@ -5829,37 +5829,37 @@
         </is>
       </c>
       <c r="T50" s="161" t="n">
-        <v>0.1604893368708296</v>
+        <v>0.160488425831654</v>
       </c>
       <c r="U50" s="162" t="n">
-        <v>0.1766843000438436</v>
+        <v>0.1766832857815186</v>
       </c>
       <c r="V50" s="162" t="n">
-        <v>0.1953625521188488</v>
+        <v>0.1953614236986136</v>
       </c>
       <c r="W50" s="162" t="n">
-        <v>0.2137483607070754</v>
+        <v>0.2137471214227699</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.230257588318819</v>
+        <v>0.2302562463217173</v>
       </c>
       <c r="Y50" s="161" t="n">
-        <v>0.1591588515303609</v>
+        <v>0.1591579555338958</v>
       </c>
       <c r="Z50" s="162" t="n">
-        <v>0.1755866562320332</v>
+        <v>0.1755856545326518</v>
       </c>
       <c r="AA50" s="162" t="n">
-        <v>0.1945355930157595</v>
+        <v>0.1945344741283615</v>
       </c>
       <c r="AB50" s="162" t="n">
-        <v>0.2132587531790543</v>
+        <v>0.2132575195655876</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.2301696430122802</v>
+        <v>0.230168302040113</v>
       </c>
       <c r="AD50" s="164" t="n">
-        <v>20304.89754058993</v>
+        <v>20304.89754058992</v>
       </c>
       <c r="AE50" s="165" t="n">
         <v>23755.19112936988</v>
@@ -5871,7 +5871,7 @@
         <v>32939.54131583038</v>
       </c>
       <c r="AH50" s="166" t="n">
-        <v>39030.04291982152</v>
+        <v>39030.04291982154</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -5881,49 +5881,49 @@
         </is>
       </c>
       <c r="C51" s="155" t="n">
-        <v>0</v>
+        <v>0.2763458705272825</v>
       </c>
       <c r="D51" s="156" t="n">
-        <v>0</v>
+        <v>0.4313018537563194</v>
       </c>
       <c r="E51" s="156" t="n">
-        <v>0</v>
+        <v>0.4513850016915925</v>
       </c>
       <c r="F51" s="156" t="n">
-        <v>0</v>
+        <v>0.45254507202636</v>
       </c>
       <c r="G51" s="157" t="n">
-        <v>0</v>
+        <v>0.4123759546608149</v>
       </c>
       <c r="H51" s="155" t="n">
-        <v>0</v>
+        <v>0.2760880259084555</v>
       </c>
       <c r="I51" s="156" t="n">
-        <v>0</v>
+        <v>0.4309398156506229</v>
       </c>
       <c r="J51" s="156" t="n">
-        <v>0</v>
+        <v>0.4510384202913938</v>
       </c>
       <c r="K51" s="156" t="n">
-        <v>0</v>
+        <v>0.452237823479231</v>
       </c>
       <c r="L51" s="157" t="n">
-        <v>0</v>
+        <v>0.4121289554098811</v>
       </c>
       <c r="M51" s="158" t="n">
-        <v>0</v>
+        <v>2565.673955526001</v>
       </c>
       <c r="N51" s="159" t="n">
-        <v>0</v>
+        <v>4515.885490353907</v>
       </c>
       <c r="O51" s="159" t="n">
-        <v>0</v>
+        <v>5276.152876196948</v>
       </c>
       <c r="P51" s="159" t="n">
-        <v>0</v>
+        <v>6062.242096718918</v>
       </c>
       <c r="Q51" s="160" t="n">
-        <v>0</v>
+        <v>6345.550780376375</v>
       </c>
       <c r="S51" s="32" t="inlineStr">
         <is>
@@ -5931,49 +5931,49 @@
         </is>
       </c>
       <c r="T51" s="155" t="n">
-        <v>0</v>
+        <v>0.1772114727185071</v>
       </c>
       <c r="U51" s="156" t="n">
-        <v>0</v>
+        <v>0.2765796230084565</v>
       </c>
       <c r="V51" s="156" t="n">
-        <v>0</v>
+        <v>0.2894582819717429</v>
       </c>
       <c r="W51" s="156" t="n">
-        <v>0</v>
+        <v>0.2902021967336641</v>
       </c>
       <c r="X51" s="157" t="n">
-        <v>0</v>
+        <v>0.2644430694756071</v>
       </c>
       <c r="Y51" s="155" t="n">
-        <v>0</v>
+        <v>0.1770884312518517</v>
       </c>
       <c r="Z51" s="156" t="n">
-        <v>0</v>
+        <v>0.2764068653552145</v>
       </c>
       <c r="AA51" s="156" t="n">
-        <v>0</v>
+        <v>0.2892929029944718</v>
       </c>
       <c r="AB51" s="156" t="n">
-        <v>0</v>
+        <v>0.2900555896338555</v>
       </c>
       <c r="AC51" s="157" t="n">
-        <v>0</v>
+        <v>0.2643252134186053</v>
       </c>
       <c r="AD51" s="158" t="n">
-        <v>0</v>
+        <v>2565.673955526001</v>
       </c>
       <c r="AE51" s="159" t="n">
-        <v>0</v>
+        <v>4515.885490353907</v>
       </c>
       <c r="AF51" s="159" t="n">
-        <v>0</v>
+        <v>5276.152876196948</v>
       </c>
       <c r="AG51" s="159" t="n">
-        <v>0</v>
+        <v>6062.242096718918</v>
       </c>
       <c r="AH51" s="160" t="n">
-        <v>0</v>
+        <v>6345.550780376375</v>
       </c>
     </row>
     <row r="52" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5983,49 +5983,49 @@
         </is>
       </c>
       <c r="C52" s="179" t="n">
-        <v>0.1277189112844412</v>
+        <v>0.1438572298697395</v>
       </c>
       <c r="D52" s="180" t="n">
-        <v>0.1399546015089556</v>
+        <v>0.1665602113626664</v>
       </c>
       <c r="E52" s="180" t="n">
-        <v>0.1541793590449602</v>
+        <v>0.1833072953094258</v>
       </c>
       <c r="F52" s="180" t="n">
-        <v>0.1679635525786575</v>
+        <v>0.198875926665184</v>
       </c>
       <c r="G52" s="181" t="n">
-        <v>0.1803508426806718</v>
+        <v>0.209672608858804</v>
       </c>
       <c r="H52" s="179" t="n">
-        <v>0.1267122917888793</v>
+        <v>0.1427234151490064</v>
       </c>
       <c r="I52" s="180" t="n">
-        <v>0.1391309354305794</v>
+        <v>0.1655799643603574</v>
       </c>
       <c r="J52" s="180" t="n">
-        <v>0.1535620636778063</v>
+        <v>0.1825733785828908</v>
       </c>
       <c r="K52" s="180" t="n">
-        <v>0.1675994946048</v>
+        <v>0.1984448664342538</v>
       </c>
       <c r="L52" s="181" t="n">
-        <v>0.1802830472300986</v>
+        <v>0.2095937910592697</v>
       </c>
       <c r="M52" s="182" t="n">
-        <v>20304.89754058993</v>
+        <v>22870.57149611592</v>
       </c>
       <c r="N52" s="183" t="n">
-        <v>23755.19112936988</v>
+        <v>28271.07661972379</v>
       </c>
       <c r="O52" s="183" t="n">
-        <v>27927.72114837499</v>
+        <v>33203.87402457194</v>
       </c>
       <c r="P52" s="183" t="n">
-        <v>32939.54131583038</v>
+        <v>39001.7834125493</v>
       </c>
       <c r="Q52" s="184" t="n">
-        <v>39030.04291982152</v>
+        <v>45375.59370019791</v>
       </c>
       <c r="S52" s="51" t="inlineStr">
         <is>
@@ -6033,49 +6033,49 @@
         </is>
       </c>
       <c r="T52" s="185" t="n">
-        <v>0.1440097299993102</v>
+        <v>0.1622055980748865</v>
       </c>
       <c r="U52" s="186" t="n">
-        <v>0.157551257161742</v>
+        <v>0.1875009482427331</v>
       </c>
       <c r="V52" s="186" t="n">
-        <v>0.1732693368414499</v>
+        <v>0.206002621176528</v>
       </c>
       <c r="W52" s="186" t="n">
-        <v>0.1882323854753557</v>
+        <v>0.2228738152653764</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.2017036616725108</v>
+        <v>0.2344956855684916</v>
       </c>
       <c r="Y52" s="185" t="n">
-        <v>0.1429274200203804</v>
+        <v>0.1609865425991591</v>
       </c>
       <c r="Z52" s="186" t="n">
-        <v>0.156667335802807</v>
+        <v>0.1864490032926799</v>
       </c>
       <c r="AA52" s="186" t="n">
-        <v>0.1726074120799669</v>
+        <v>0.205215652503935</v>
       </c>
       <c r="AB52" s="186" t="n">
-        <v>0.1878412789509085</v>
+        <v>0.2224107336392902</v>
       </c>
       <c r="AC52" s="187" t="n">
-        <v>0.2016250280917121</v>
+        <v>0.2344042685799228</v>
       </c>
       <c r="AD52" s="188" t="n">
-        <v>20304.89754058993</v>
+        <v>22870.57149611592</v>
       </c>
       <c r="AE52" s="189" t="n">
-        <v>23755.19112936988</v>
+        <v>28271.07661972379</v>
       </c>
       <c r="AF52" s="189" t="n">
-        <v>27927.72114837499</v>
+        <v>33203.87402457194</v>
       </c>
       <c r="AG52" s="189" t="n">
-        <v>32939.54131583038</v>
+        <v>39001.7834125493</v>
       </c>
       <c r="AH52" s="190" t="n">
-        <v>39030.04291982152</v>
+        <v>45375.59370019791</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,46 +6334,46 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.009134474629031433</v>
+        <v>0.00927178594679906</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.008427161539577902</v>
+        <v>0.008673001597181177</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007816542830861766</v>
+        <v>0.008154209771444258</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.000285387928371577</v>
+        <v>0.0003025074422220581</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.009057096496587265</v>
+        <v>0.009193244583315751</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.008374080871606484</v>
+        <v>0.008618372396580993</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.007783103765306706</v>
+        <v>0.008119326143140336</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.0002847404443409758</v>
+        <v>0.0003018211171499737</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1053.898963840929</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1041.046932957326</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1030.078222867857</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>40.54591548586917</v>
+        <v>42.97810241174496</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6384,46 +6384,46 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.01120897928773414</v>
+        <v>0.01137737830863673</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.01034103032606862</v>
+        <v>0.01064261198530012</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.009591735732053431</v>
+        <v>0.01000600422723652</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003502015723947065</v>
+        <v>0.0003712058961549507</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.01111509316438934</v>
+        <v>0.01128208240124045</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01027662691503181</v>
+        <v>0.01057633084401817</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.009551164640306455</v>
+        <v>0.009963681188025946</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.0003494160080708724</v>
+        <v>0.0003703732218139359</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1053.898963840929</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1041.046932957326</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1030.078222867857</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>40.54591548586917</v>
+        <v>42.97810241174496</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6538,46 +6538,46 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.00746852663701203</v>
+        <v>0.00758079389121675</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.006939487022876807</v>
+        <v>0.007141927079656489</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006461917311996158</v>
+        <v>0.006741064821206356</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002362608153244657</v>
+        <v>0.0002504333163143451</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.007404661817297584</v>
+        <v>0.007515969007297075</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.006894796644189209</v>
+        <v>0.007095932953333773</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006433230445747455</v>
+        <v>0.006711138694901172</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.0002356882779444493</v>
+        <v>0.0002498264339287945</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1053.898963840929</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1041.046932957326</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1030.078222867857</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>40.54591548586917</v>
+        <v>42.97810241174496</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6588,46 +6588,46 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.008821909227682301</v>
+        <v>0.008954460471825448</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008206842140705094</v>
+        <v>0.008446196555987591</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007647126988212647</v>
+        <v>0.007977419977099344</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002796611883593647</v>
+        <v>0.0002964351150795157</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.008746877430954359</v>
+        <v>0.008878301758812861</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.008154157890763644</v>
+        <v>0.008391976085712754</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.007613197244297585</v>
+        <v>0.007942024963322256</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.0002789803958795939</v>
+        <v>0.0002957134934715717</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1053.898963840929</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1041.046932957326</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1030.078222867857</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>40.54591548586917</v>
+        <v>42.97810241174496</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,46 +6742,46 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.007040221379223673</v>
+        <v>0.007146050040203294</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006536586386055866</v>
+        <v>0.006727272680318344</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.006078984423487143</v>
+        <v>0.006341589414292297</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002219075385080904</v>
+        <v>0.0002352190248977189</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.006981722143652397</v>
+        <v>0.007086671404693649</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.006495960355949302</v>
+        <v>0.0066854614746883</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.006053293453453058</v>
+        <v>0.00631478860772193</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.000221402379032236</v>
+        <v>0.0002346835622808183</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1053.898963840929</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1041.046932957326</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1030.078222867857</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>40.54591548586917</v>
+        <v>42.97810241174496</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6792,46 +6792,46 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008329987654336672</v>
+        <v>0.00845515049649951</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007743008576973478</v>
+        <v>0.007968837921315749</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007205697501502813</v>
+        <v>0.007516927027122751</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002631069718116285</v>
+        <v>0.0002788880873185864</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.008260930565084063</v>
+        <v>0.008385056179477123</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007694905460583392</v>
+        <v>0.007919332132010884</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.007175196174209797</v>
+        <v>0.007485108465110811</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.000262504304480531</v>
+        <v>0.0002782492757893911</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1053.898963840929</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1041.046932957326</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1030.078222867857</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>40.54591548586917</v>
+        <v>42.97810241174496</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6844,49 +6844,49 @@
         </is>
       </c>
       <c r="C62" s="155" t="n">
-        <v>0</v>
+        <v>0.2700315068077224</v>
       </c>
       <c r="D62" s="156" t="n">
-        <v>0</v>
+        <v>0.4145803792878787</v>
       </c>
       <c r="E62" s="156" t="n">
-        <v>0</v>
+        <v>0.4233656501664354</v>
       </c>
       <c r="F62" s="156" t="n">
-        <v>0</v>
+        <v>0.4133032004320717</v>
       </c>
       <c r="G62" s="157" t="n">
-        <v>0</v>
+        <v>0.366737282027258</v>
       </c>
       <c r="H62" s="155" t="n">
-        <v>0</v>
+        <v>0.2697795538083478</v>
       </c>
       <c r="I62" s="156" t="n">
-        <v>0</v>
+        <v>0.4142323773169409</v>
       </c>
       <c r="J62" s="156" t="n">
-        <v>0</v>
+        <v>0.4230405825206768</v>
       </c>
       <c r="K62" s="156" t="n">
-        <v>0</v>
+        <v>0.4130225945527768</v>
       </c>
       <c r="L62" s="157" t="n">
-        <v>0</v>
+        <v>0.3665176187978034</v>
       </c>
       <c r="M62" s="158" t="n">
-        <v>0</v>
+        <v>2507.049600075774</v>
       </c>
       <c r="N62" s="159" t="n">
-        <v>0</v>
+        <v>4340.80564019398</v>
       </c>
       <c r="O62" s="159" t="n">
-        <v>0</v>
+        <v>4948.640039960449</v>
       </c>
       <c r="P62" s="159" t="n">
-        <v>0</v>
+        <v>5536.562466913832</v>
       </c>
       <c r="Q62" s="160" t="n">
-        <v>0</v>
+        <v>5643.272891784613</v>
       </c>
       <c r="S62" s="32" t="inlineStr">
         <is>
@@ -6894,49 +6894,49 @@
         </is>
       </c>
       <c r="T62" s="155" t="n">
-        <v>0</v>
+        <v>0.173162279973602</v>
       </c>
       <c r="U62" s="156" t="n">
-        <v>0</v>
+        <v>0.2658566941261711</v>
       </c>
       <c r="V62" s="156" t="n">
-        <v>0</v>
+        <v>0.2714903979613306</v>
       </c>
       <c r="W62" s="156" t="n">
-        <v>0</v>
+        <v>0.2650376815404912</v>
       </c>
       <c r="X62" s="157" t="n">
-        <v>0</v>
+        <v>0.235176497209198</v>
       </c>
       <c r="Y62" s="155" t="n">
-        <v>0</v>
+        <v>0.1730420499423828</v>
       </c>
       <c r="Z62" s="156" t="n">
-        <v>0</v>
+        <v>0.2656906342477305</v>
       </c>
       <c r="AA62" s="156" t="n">
-        <v>0</v>
+        <v>0.2713352847476131</v>
       </c>
       <c r="AB62" s="156" t="n">
-        <v>0</v>
+        <v>0.264903787289283</v>
       </c>
       <c r="AC62" s="157" t="n">
-        <v>0</v>
+        <v>0.2350716845751761</v>
       </c>
       <c r="AD62" s="158" t="n">
-        <v>0</v>
+        <v>2507.049600075774</v>
       </c>
       <c r="AE62" s="159" t="n">
-        <v>0</v>
+        <v>4340.80564019398</v>
       </c>
       <c r="AF62" s="159" t="n">
-        <v>0</v>
+        <v>4948.640039960449</v>
       </c>
       <c r="AG62" s="159" t="n">
-        <v>0</v>
+        <v>5536.562466913832</v>
       </c>
       <c r="AH62" s="160" t="n">
-        <v>0</v>
+        <v>5643.272891784613</v>
       </c>
     </row>
     <row r="63" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006629081875271232</v>
+        <v>0.02249821836726506</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006133367139026158</v>
+        <v>0.03188632547812056</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005686708175155883</v>
+        <v>0.03325212559895742</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002067495701370822</v>
+        <v>0.02845091183019014</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0</v>
+        <v>0.02607656789111029</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.006576834616144015</v>
+        <v>0.02232089803933875</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.00609727081633169</v>
+        <v>0.03169866676474083</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005663940026211533</v>
+        <v>0.03311899237516115</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.0002063014441690109</v>
+        <v>0.02838924495663061</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0</v>
+        <v>0.02606676547718616</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1053.898963840929</v>
+        <v>3576.790072835954</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1041.046932957326</v>
+        <v>5412.221462366942</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1030.078222867857</v>
+        <v>6023.215756761276</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>40.54591548586917</v>
+        <v>5579.540569325577</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>0</v>
+        <v>5643.272891784613</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.00747463536449224</v>
+        <v>0.02536776892747098</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006904522559240425</v>
+        <v>0.03589522500128217</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006390817554461226</v>
+        <v>0.03736908027317406</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002316988667209959</v>
+        <v>0.03188401619894694</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0</v>
+        <v>0.02916376487220144</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.007418459490515598</v>
+        <v>0.0251771175690404</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.006865785610559045</v>
+        <v>0.03569384041616402</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006366403307471356</v>
+        <v>0.03722632337362276</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.000231217446171324</v>
+        <v>0.03181776838939612</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0</v>
+        <v>0.02915239552204269</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1053.898963840929</v>
+        <v>3576.790072835954</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1041.046932957326</v>
+        <v>5412.221462366942</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1030.078222867857</v>
+        <v>6023.215756761276</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>40.54591548586917</v>
+        <v>5579.540569325577</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>0</v>
+        <v>5643.272891784613</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.00387705391140012</v>
+        <v>0.003935334590174849</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005648641485182503</v>
+        <v>0.005813425599213744</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.007486889664913953</v>
+        <v>0.007810315913875151</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.009182457773196494</v>
+        <v>0.009733284200672491</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.01067634595395877</v>
+        <v>0.01149457509335657</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.003844211388624258</v>
+        <v>0.003901998343388212</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.005613062048173209</v>
+        <v>0.005776808196383229</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.007454860851188261</v>
+        <v>0.007776903460073687</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.009161624744961069</v>
+        <v>0.009711201448157132</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.01067378824316287</v>
+        <v>0.01149182135901355</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>447.3188952754543</v>
+        <v>454.0426956703517</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>697.8032717074625</v>
+        <v>718.1592322140588</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>986.6359294281567</v>
+        <v>1029.256795794545</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>1304.579205395948</v>
+        <v>1382.835682012913</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1668.030559564992</v>
+        <v>1795.866156071027</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004757560643082173</v>
+        <v>0.004829036246133422</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006931488452550456</v>
+        <v>0.007133635600615035</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.009187215969362183</v>
+        <v>0.00958401319573186</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.01126785974785356</v>
+        <v>0.01194368131144775</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01310102064176375</v>
+        <v>0.01410495562392703</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.004717711437022387</v>
+        <v>0.004788588668629959</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.00688831949492917</v>
+        <v>0.007089208019326592</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.009148355913955663</v>
+        <v>0.009543475079110488</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.01124258393723012</v>
+        <v>0.01191688971931973</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.01309791755329573</v>
+        <v>0.01410161477081343</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>447.3188952754543</v>
+        <v>454.0426956703517</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>697.8032717074625</v>
+        <v>718.1592322140588</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>986.6359294281567</v>
+        <v>1029.256795794545</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>1304.579205395948</v>
+        <v>1382.835682012913</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1668.030559564992</v>
+        <v>1795.866156071027</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003169955754039222</v>
+        <v>0.003217606682495817</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004651468243395145</v>
+        <v>0.004787161774083734</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.006189393826091116</v>
+        <v>0.006456768629366118</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.0076017754939979</v>
+        <v>0.008057780737887224</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008849180990644658</v>
+        <v>0.009527376032760843</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.003142848847607208</v>
+        <v>0.003190092284573243</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.004621512732769448</v>
+        <v>0.004756332374552105</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.006161916793458711</v>
+        <v>0.006428104600959522</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.007583353900815681</v>
+        <v>0.008038254081975697</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.008845794665438658</v>
+        <v>0.009523730179729186</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>447.3188952754543</v>
+        <v>454.0426956703517</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>697.8032717074625</v>
+        <v>718.1592322140588</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>986.6359294281567</v>
+        <v>1029.256795794545</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>1304.579205395948</v>
+        <v>1382.835682012913</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1668.030559564992</v>
+        <v>1795.866156071027</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003744388053637757</v>
+        <v>0.003800648357643947</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005500963611604473</v>
+        <v>0.005661400464924128</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007324618728919793</v>
+        <v>0.007640982013609516</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.008998197883017303</v>
+        <v>0.009537904922054823</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.01047690116916105</v>
+        <v>0.01127976665172878</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.003712541414088407</v>
+        <v>0.003768323407587794</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.005465649889607172</v>
+        <v>0.005625057029913164</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.007292119930595823</v>
+        <v>0.007607079741393866</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.008976293143621087</v>
+        <v>0.009514686490984589</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.01047264092237668</v>
+        <v>0.01127517996232831</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>447.3188952754543</v>
+        <v>454.0426956703517</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>697.8032717074625</v>
+        <v>718.1592322140588</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>986.6359294281567</v>
+        <v>1029.256795794545</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>1304.579205395948</v>
+        <v>1382.835682012913</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1668.030559564992</v>
+        <v>1795.866156071027</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.008690064678311177</v>
+        <v>0.008829475055652744</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01266890429561433</v>
+        <v>0.0130201614973281</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.01662674882489198</v>
+        <v>0.01726845000666725</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.02013203964405095</v>
+        <v>0.02113694321030983</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.0230512031623378</v>
+        <v>0.02445839321279067</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.008652558177116375</v>
+        <v>0.008791366856348909</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.01263655807645514</v>
+        <v>0.01298691844903809</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.01661295288206362</v>
+        <v>0.0172541216162203</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.02013203964405095</v>
+        <v>0.02113694321030983</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.0230512031623378</v>
+        <v>0.02445839321279067</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>74.60263068385404</v>
+        <v>75.79944351313794</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>117.1463995275705</v>
+        <v>120.3943928448097</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>166.9582110181674</v>
+        <v>173.4018809409996</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>223.4715256823137</v>
+        <v>234.6262490529201</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>288.7970884033706</v>
+        <v>306.4270744192399</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01057465574841193</v>
+        <v>0.01074429968119216</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.01541637566519635</v>
+        <v>0.01584380907619778</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.02023254734540302</v>
+        <v>0.02101341254512456</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.02449802120351918</v>
+        <v>0.02572085551683114</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.02805025590163947</v>
+        <v>0.02976261949235803</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.01052563708375766</v>
+        <v>0.01069449463452703</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.01537409562759671</v>
+        <v>0.01580035678507494</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.0202145122319452</v>
+        <v>0.02099468137534561</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.02449802120351918</v>
+        <v>0.02572085551683114</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.02805025590163947</v>
+        <v>0.02976261949235803</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>74.60263068385404</v>
+        <v>75.79944351313794</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>117.1463995275705</v>
+        <v>120.3943928448097</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>166.9582110181674</v>
+        <v>173.4018809409996</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>223.4715256823137</v>
+        <v>234.6262490529201</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>288.7970884033706</v>
+        <v>306.4270744192399</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.003486523102693146</v>
+        <v>0.003539436467467755</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005116953671995481</v>
+        <v>0.005265162951765485</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006807910948039581</v>
+        <v>0.007097468716396225</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.008363011967684915</v>
+        <v>0.008852364271218173</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.009734299733295631</v>
+        <v>0.01045792877915433</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.003457552573881219</v>
+        <v>0.003510026246894302</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.005085150908036629</v>
+        <v>0.005232439020194223</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.006779139392796729</v>
+        <v>0.007067473414937782</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.008343974062210576</v>
+        <v>0.008832212371768355</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.009730806772413062</v>
+        <v>0.01045417615615192</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>521.9215259593084</v>
+        <v>529.8421391834897</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>814.9496712350331</v>
+        <v>838.5536250588684</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>1153.594140446324</v>
+        <v>1202.658676735545</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1528.050731078261</v>
+        <v>1617.461931065833</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1956.827647968362</v>
+        <v>2102.293230490267</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004125253005211043</v>
+        <v>0.004187833535571926</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.00606136197553472</v>
+        <v>0.006236885612603128</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.008069727357617108</v>
+        <v>0.008412899500903881</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.009915691773408432</v>
+        <v>0.01049583017751627</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.01154429719440448</v>
+        <v>0.01240239855525271</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.004091053919114902</v>
+        <v>0.004153115841120373</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.006023706018203267</v>
+        <v>0.006198139443073168</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.008035568638735452</v>
+        <v>0.008377288357746064</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.009892979097055088</v>
+        <v>0.01047178878732876</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.01153988792927255</v>
+        <v>0.01239766157178956</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>521.9215259593084</v>
+        <v>529.8421391834897</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>814.9496712350331</v>
+        <v>838.5536250588684</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>1153.594140446324</v>
+        <v>1202.658676735545</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1528.050731078261</v>
+        <v>1617.461931065833</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1956.827647968362</v>
+        <v>2102.293230490267</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>0</v>
+        <v>0.9007754759547962</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>0</v>
+        <v>1.382963947019975</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>0</v>
+        <v>1.412269995971731</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>0</v>
+        <v>1.37870351309758</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>0</v>
+        <v>1.22336816793641</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>0</v>
+        <v>0.8999350070568781</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>0</v>
+        <v>1.381803076406355</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>0</v>
+        <v>1.411185630051667</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>0</v>
+        <v>1.377767463458537</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>0</v>
+        <v>1.222635411776209</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>0</v>
+        <v>8363.056679747247</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>0</v>
+        <v>14480.12979225125</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>0</v>
+        <v>16507.75363223968</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>0</v>
+        <v>18468.95479066795</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>0</v>
+        <v>18824.92115506986</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>0</v>
+        <v>0.5776375394287073</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>0</v>
+        <v>0.8868490681637078</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>0</v>
+        <v>0.9056420687046318</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>0</v>
+        <v>0.8841169927092531</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>0</v>
+        <v>0.7845055701512639</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>0</v>
+        <v>0.5772364741423789</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>0</v>
+        <v>0.8862951229303992</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>0</v>
+        <v>0.9051246395328845</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>0</v>
+        <v>0.8836703460964724</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>0</v>
+        <v>0.784155934468327</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>0</v>
+        <v>8363.056679747247</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>0</v>
+        <v>14480.12979225125</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>0</v>
+        <v>16507.75363223968</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>0</v>
+        <v>18468.95479066795</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>0</v>
+        <v>18824.92115506986</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.00328291482082999</v>
+        <v>0.05593685272886673</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004801306622472913</v>
+        <v>0.09025065377258613</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006368597145004975</v>
+        <v>0.09777316275716912</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.007791754804702553</v>
+        <v>0.1024236429566067</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.009042150325504816</v>
+        <v>0.09670096363606913</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.003257040453223169</v>
+        <v>0.05549598488292744</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.004773049792371041</v>
+        <v>0.08971950691528316</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.006343098884166214</v>
+        <v>0.09738170338053824</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.007774866316554709</v>
+        <v>0.1022016414307009</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.009038751302542924</v>
+        <v>0.0966646128833021</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>521.9215259593084</v>
+        <v>8892.898818930737</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>814.9496712350331</v>
+        <v>15318.68341731012</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>1153.594140446324</v>
+        <v>17710.41230897523</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1528.050731078261</v>
+        <v>20086.41672173378</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1956.827647968362</v>
+        <v>20927.21438556013</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003701657586992398</v>
+        <v>0.06307135664664464</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005404980516779935</v>
+        <v>0.1015973924591182</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.007157135759032291</v>
+        <v>0.1098784845125607</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008732016984704983</v>
+        <v>0.1147828621688776</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.01011270478661904</v>
+        <v>0.1081493614563839</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.0036738376546517</v>
+        <v>0.06259734413663157</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.005374656558663215</v>
+        <v>0.1010273960674328</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.007129794017749273</v>
+        <v>0.1094587280812613</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.008713873726276434</v>
+        <v>0.1145443692153797</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.01010876237832393</v>
+        <v>0.1081071999602523</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>521.9215259593084</v>
+        <v>8892.898818930737</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>814.9496712350331</v>
+        <v>15318.68341731012</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>1153.594140446324</v>
+        <v>17710.41230897523</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1528.050731078261</v>
+        <v>20086.41672173378</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1956.827647968362</v>
+        <v>20927.21438556013</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>466.6855544579347</v>
+        <v>460.8784740263726</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>504.946761709972</v>
+        <v>493.6285562268444</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>540.5472992174532</v>
+        <v>524.0452590173888</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>574.7344795210607</v>
+        <v>552.5626407707824</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>606.8686872348549</v>
+        <v>578.5641850339014</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>462.7322612353714</v>
+        <v>456.9743692554213</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>501.7662232480366</v>
+        <v>490.5193058574152</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>538.2348451101493</v>
+        <v>521.8033986112446</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>573.4305301933887</v>
+        <v>551.3089936159473</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>606.7233009201244</v>
+        <v>578.425579469709</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>53844303.28588021</v>
+        <v>53174260.00976323</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>62378450.33776695</v>
+        <v>60980208.46551316</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>71234305.67737924</v>
+        <v>69059580.95617466</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>81654244.33487281</v>
+        <v>78504163.69762713</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>94814791.53225426</v>
+        <v>90392540.00939244</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>572.6731887982029</v>
+        <v>565.5424729812186</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>619.6237904506227</v>
+        <v>605.7299920818245</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>663.3094651894086</v>
+        <v>643.0542289154912</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>705.2607991732219</v>
+        <v>678.0478150963916</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>744.6929157775965</v>
+        <v>709.9542252947847</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>567.8764928404714</v>
+        <v>560.8055395971043</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>615.7648049911201</v>
+        <v>601.9575652340412</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>660.503801030115</v>
+        <v>640.3342611114764</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>703.6787739440355</v>
+        <v>676.5268451348146</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>744.5165289095537</v>
+        <v>709.7860678863299</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>53844303.28588021</v>
+        <v>53174260.00976323</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>62378450.33776695</v>
+        <v>60980208.46551316</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>71234305.67737924</v>
+        <v>69059580.95617466</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>81654244.33487281</v>
+        <v>78504163.69762713</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>94814791.53225426</v>
+        <v>90392540.00939244</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>1046.529579090465</v>
+        <v>1029.220716820228</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>1126.574450002636</v>
+        <v>1095.363081260288</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1204.017802653421</v>
+        <v>1159.517628447959</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1272.632962688617</v>
+        <v>1214.312887632912</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1334.413639823041</v>
+        <v>1262.062596963041</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>1037.2044260151</v>
+        <v>1020.049795209941</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>1118.577604657871</v>
+        <v>1087.587785844009</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>1197.746659998266</v>
+        <v>1153.478265538923</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>1268.603960540155</v>
+        <v>1210.468519793467</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1332.978935541728</v>
+        <v>1260.705681418183</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>26933538.63435649</v>
+        <v>26488076.8719882</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>29835233.6544558</v>
+        <v>29008658.47418153</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>33261839.11560193</v>
+        <v>32032490.48655646</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>37596223.68710625</v>
+        <v>35873327.41494709</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>43047359.62179434</v>
+        <v>40713359.67750474</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>1058.663462971985</v>
+        <v>1041.15391480705</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1139.636406237165</v>
+        <v>1108.063160361414</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1217.977668194323</v>
+        <v>1172.961541112512</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1287.388379928213</v>
+        <v>1228.392118520182</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1349.885367024102</v>
+        <v>1276.695457140838</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>1049.15420339551</v>
+        <v>1031.801931687533</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>1131.481559061162</v>
+        <v>1100.134240501841</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1211.582521945054</v>
+        <v>1166.802757748854</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1283.279641349469</v>
+        <v>1224.471668276977</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1348.422244199315</v>
+        <v>1275.311663887517</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>26933538.63435649</v>
+        <v>26488076.8719882</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>29835233.6544558</v>
+        <v>29008658.47418153</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>33261839.11560193</v>
+        <v>32032490.48655646</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>37596223.68710625</v>
+        <v>35873327.41494709</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>43047359.62179434</v>
+        <v>40713359.67750474</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>572.4376669495362</v>
+        <v>564.5329611910632</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>614.6847400797481</v>
+        <v>599.8548018086464</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>655.5283201645216</v>
+        <v>634.1742102029887</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>694.8717883189989</v>
+        <v>666.4774106734119</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>731.3817605595575</v>
+        <v>695.5391426069557</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>567.5426414412498</v>
+        <v>559.7055269931171</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>610.7261630671976</v>
+        <v>595.9917271479902</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>652.618184931456</v>
+        <v>631.3588719712122</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>693.1878862610756</v>
+        <v>664.8623164564851</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>731.1018819477842</v>
+        <v>695.2729797639032</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>80777841.92023669</v>
+        <v>79662336.88175143</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>92213683.99222276</v>
+        <v>89988866.93969469</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>104496144.7929812</v>
+        <v>101092071.4427311</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>119250468.0219791</v>
+        <v>114377491.1125742</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>137862151.1540486</v>
+        <v>131105899.6868972</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>676.1699303994739</v>
+        <v>666.8283241264302</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>726.9443132474588</v>
+        <v>709.4011888696705</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>775.7617540790336</v>
+        <v>750.4858872621204</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>822.5175631084207</v>
+        <v>788.9018555457816</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>865.9122726058379</v>
+        <v>823.4711423976927</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>670.4189933333702</v>
+        <v>661.1568727725939</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>722.2776564218465</v>
+        <v>704.84717857414</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>772.3197558363507</v>
+        <v>747.1560565154119</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>820.5152696377796</v>
+        <v>786.9814061909328</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>865.560164676656</v>
+        <v>823.1362944813261</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>80777841.92023669</v>
+        <v>79662336.88175143</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>92213683.99222276</v>
+        <v>89988866.93969469</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>104496144.7929812</v>
+        <v>101092071.4427311</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>119250468.0219791</v>
+        <v>114377491.1125742</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>137862151.1540486</v>
+        <v>131105899.6868972</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>1213.105812026243</v>
+        <v>1192.609081967945</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>1295.392884503767</v>
+        <v>1259.453427554498</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1366.719122978157</v>
+        <v>1316.223157963662</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1425.325714617607</v>
+        <v>1360.063968947291</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1465.925862055849</v>
+        <v>1386.480554818694</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>1207.870021928875</v>
+        <v>1187.461756186883</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>1292.085490181283</v>
+        <v>1256.237793776084</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>1365.585096171016</v>
+        <v>1315.131029873686</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>1425.325714617606</v>
+        <v>1360.06396894729</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1465.925862055849</v>
+        <v>1386.480554818694</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>10414293.58988598</v>
+        <v>10238332.87620082</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>11978195.4975998</v>
+        <v>11645871.73191783</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>13723968.6567668</v>
+        <v>13216911.25960239</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>15821532.12846238</v>
+        <v>15097107.67214823</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>18365857.85980269</v>
+        <v>17370527.01933324</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1476.188822920045</v>
+        <v>1451.247021868139</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1576.321272585948</v>
+        <v>1532.587721790646</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1663.115841512263</v>
+        <v>1601.668951704313</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1734.43228783535</v>
+        <v>1655.0174020375</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1783.837280592851</v>
+        <v>1687.162882189754</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>1469.345970859544</v>
+        <v>1444.519787167742</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>1571.998147350716</v>
+        <v>1528.384537598117</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>1661.633354785154</v>
+        <v>1600.241238190403</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>1734.43228783535</v>
+        <v>1655.0174020375</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1783.837280592851</v>
+        <v>1687.162882189754</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>10414293.58988598</v>
+        <v>10238332.87620082</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>11978195.4975998</v>
+        <v>11645871.73191783</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>13723968.6567668</v>
+        <v>13216911.25960239</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>15821532.12846238</v>
+        <v>15097107.67214823</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>18365857.85980269</v>
+        <v>17370527.01933324</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>609.1787202215438</v>
+        <v>600.5519105774194</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>654.2060683816119</v>
+        <v>638.1505543292765</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>697.6734506657881</v>
+        <v>674.5924212970101</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>739.2482008500973</v>
+        <v>708.6140887142367</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>777.1610688635506</v>
+        <v>738.6010064423668</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>604.1168780521463</v>
+        <v>595.5617477878817</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>650.1400629989453</v>
+        <v>634.1843342401087</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>694.7249470234068</v>
+        <v>671.7414607860268</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>737.565345746668</v>
+        <v>707.0009693907444</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>776.8821999888116</v>
+        <v>738.335973931158</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>91192135.51012267</v>
+        <v>89900669.75795226</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>104191879.4898226</v>
+        <v>101634738.6716125</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>118220113.449748</v>
+        <v>114308982.7023335</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>135072000.1504415</v>
+        <v>129474598.7847224</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>156228009.0138513</v>
+        <v>148476426.7062304</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>720.7800643464473</v>
+        <v>710.5683218456644</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>774.9493236091724</v>
+        <v>755.9257039967584</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>826.9841621741652</v>
+        <v>799.6200435984179</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>876.4972873410177</v>
+        <v>840.1702538068515</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>921.6665392164167</v>
+        <v>875.9310039927193</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>714.8046685474919</v>
+        <v>704.677616382984</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>770.1349834028541</v>
+        <v>751.229574021258</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>823.483583001732</v>
+        <v>796.2353147256453</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>874.4896009720899</v>
+        <v>838.2457885140557</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>921.3145150034052</v>
+        <v>875.5964501028177</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>91192135.51012267</v>
+        <v>89900669.75795226</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>104191879.4898226</v>
+        <v>101634738.6716125</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>118220113.449748</v>
+        <v>114308982.7023335</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>135072000.1504415</v>
+        <v>129474598.7847224</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>156228009.0138513</v>
+        <v>148476426.7062304</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>7068.508411328544</v>
+        <v>6943.513463418563</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>7363.990971797621</v>
+        <v>7144.450671552171</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>8030.116030518208</v>
+        <v>7667.430306855867</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>8456.934017748536</v>
+        <v>7958.184273087458</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>9009.113228766104</v>
+        <v>8362.620863699289</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>7061.913136886711</v>
+        <v>6937.034815560068</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>7357.809580925831</v>
+        <v>7138.453564503261</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>8023.95036518333</v>
+        <v>7661.543118044285</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>8451.192311892621</v>
+        <v>7952.781185733656</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>9003.717074616156</v>
+        <v>8357.611936612655</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>65626050.06819405</v>
+        <v>64465561.28718544</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>77103633.31623124</v>
+        <v>74804967.43341196</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>93862489.07659048</v>
+        <v>89623125.08158542</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>113288122.1797575</v>
+        <v>106606927.5657632</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>138630259.1922878</v>
+        <v>128682176.416629</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>4532.800809017408</v>
+        <v>4452.64568037649</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>4722.284008471227</v>
+        <v>4581.500070381882</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>5149.447991219879</v>
+        <v>4916.869624474081</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>5423.152258830303</v>
+        <v>5103.320532737465</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>5777.246535695231</v>
+        <v>5362.672350467988</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>4529.653594838537</v>
+        <v>4449.554119505142</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4719.334367082712</v>
+        <v>4578.638365705746</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>5146.505907695795</v>
+        <v>4914.060422179603</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>5420.412539305653</v>
+        <v>5100.742388839454</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>5774.671752781181</v>
+        <v>5360.282333518508</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>65626050.06819405</v>
+        <v>64465561.28718544</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>77103633.31623124</v>
+        <v>74804967.43341196</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>93862489.07659048</v>
+        <v>89623125.08158542</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>113288122.1797575</v>
+        <v>106606927.5657632</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>138630259.1922878</v>
+        <v>128682176.416629</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>986.3949272152875</v>
+        <v>970.9726050071386</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>1068.109328691646</v>
+        <v>1039.501789652988</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>1170.835226704508</v>
+        <v>1125.839806432117</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>1266.424691997827</v>
+        <v>1203.815010838116</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1362.487283234171</v>
+        <v>1280.700981421612</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>978.6206332280256</v>
+        <v>963.3198576688055</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>1061.823251545521</v>
+        <v>1033.384070992176</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>1166.147497000465</v>
+        <v>1121.332224429204</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>1263.679739296282</v>
+        <v>1201.20576202017</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>1361.975112412598</v>
+        <v>1280.219554525813</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>156818185.5783167</v>
+        <v>154366231.0451377</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>181295512.8060538</v>
+        <v>176439706.1050245</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>212082602.5263384</v>
+        <v>203932107.7839189</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>248360122.3301989</v>
+        <v>236081526.3504856</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>294858268.2061391</v>
+        <v>277158603.1228594</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>1112.2116976444</v>
+        <v>1094.815966163986</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>1202.403963193628</v>
+        <v>1170.192866984082</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>1315.804168199584</v>
+        <v>1265.230337714581</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>1419.249218892348</v>
+        <v>1349.076526446128</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1523.800332317582</v>
+        <v>1432.322783034284</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>1103.85283314928</v>
+        <v>1086.587881472052</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>1195.658028160918</v>
+        <v>1163.627681642093</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>1310.777523692998</v>
+        <v>1260.396920383728</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>1416.300323419747</v>
+        <v>1346.273449059772</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>1523.206283228147</v>
+        <v>1431.764399048813</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>156818185.5783167</v>
+        <v>154366231.0451377</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>181295512.8060538</v>
+        <v>176439706.1050245</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>212082602.5263384</v>
+        <v>203932107.7839189</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>248360122.3301989</v>
+        <v>236081526.3504856</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>294858268.2061391</v>
+        <v>277158603.1228594</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9281,22 +9281,22 @@
         </is>
       </c>
       <c r="C90" s="74" t="n">
-        <v>115375.9801895337</v>
+        <v>115375.8810760176</v>
       </c>
       <c r="D90" s="75" t="n">
-        <v>123534.7071570992</v>
+        <v>123534.6045043027</v>
       </c>
       <c r="E90" s="75" t="n">
-        <v>131781.8177623025</v>
+        <v>131781.7111553778</v>
       </c>
       <c r="F90" s="75" t="n">
-        <v>142072.9871695138</v>
+        <v>142072.8762771943</v>
       </c>
       <c r="G90" s="76" t="n">
-        <v>156236.0911456311</v>
+        <v>156235.9757960058</v>
       </c>
       <c r="H90" s="74" t="n">
-        <v>985.6997636433864</v>
+        <v>985.6997636334097</v>
       </c>
       <c r="I90" s="75" t="n">
         <v>783.0477008869115</v>
@@ -9311,19 +9311,19 @@
         <v>37.4381361076853</v>
       </c>
       <c r="M90" s="74" t="n">
-        <v>116361.6799531771</v>
+        <v>116361.580839651</v>
       </c>
       <c r="N90" s="75" t="n">
-        <v>124317.7548579861</v>
+        <v>124317.6522051896</v>
       </c>
       <c r="O90" s="75" t="n">
-        <v>132348.0007371154</v>
+        <v>132347.8941301906</v>
       </c>
       <c r="P90" s="75" t="n">
-        <v>142396.0532888527</v>
+        <v>142395.9423965332</v>
       </c>
       <c r="Q90" s="76" t="n">
-        <v>156273.5292817388</v>
+        <v>156273.4139321135</v>
       </c>
       <c r="S90" s="21" t="inlineStr">
         <is>
@@ -9331,22 +9331,22 @@
         </is>
       </c>
       <c r="T90" s="74" t="n">
-        <v>94022.74165982254</v>
+        <v>94023.45986404654</v>
       </c>
       <c r="U90" s="75" t="n">
-        <v>100671.4901834258</v>
+        <v>100672.262002301</v>
       </c>
       <c r="V90" s="75" t="n">
-        <v>107392.2647207186</v>
+        <v>107393.0904282263</v>
       </c>
       <c r="W90" s="75" t="n">
-        <v>115778.7933635276</v>
+        <v>115779.6868447499</v>
       </c>
       <c r="X90" s="76" t="n">
-        <v>127320.6573118131</v>
+        <v>127321.6452396772</v>
       </c>
       <c r="Y90" s="74" t="n">
-        <v>794.1841413414386</v>
+        <v>794.1841413334002</v>
       </c>
       <c r="Z90" s="75" t="n">
         <v>630.9061733560982</v>
@@ -9361,22 +9361,22 @@
         <v>30.16412813999912</v>
       </c>
       <c r="AD90" s="74" t="n">
-        <v>94816.92580116398</v>
+        <v>94817.64400537995</v>
       </c>
       <c r="AE90" s="75" t="n">
-        <v>101302.3963567819</v>
+        <v>101303.1681756571</v>
       </c>
       <c r="AF90" s="75" t="n">
-        <v>107848.4416990227</v>
+        <v>107849.2674065304</v>
       </c>
       <c r="AG90" s="75" t="n">
-        <v>116039.0896505383</v>
+        <v>116039.9831317606</v>
       </c>
       <c r="AH90" s="76" t="n">
-        <v>127350.8214399531</v>
+        <v>127351.8093678172</v>
       </c>
       <c r="AJ90" s="113" t="n">
-        <v>24.44774246044112</v>
+        <v>24.44795020948028</v>
       </c>
       <c r="AK90" s="114" t="n">
         <v>24.17117779573997</v>
@@ -9388,7 +9388,7 @@
         <v>30</v>
       </c>
       <c r="AN90" s="117" t="n">
-        <v>1.227107167401775</v>
+        <v>1.22709673992901</v>
       </c>
       <c r="AO90" s="118" t="n">
         <v>1.241147628531669</v>
@@ -9524,22 +9524,22 @@
         </is>
       </c>
       <c r="C92" s="85" t="n">
-        <v>141112.0312027925</v>
+        <v>141111.9320892764</v>
       </c>
       <c r="D92" s="86" t="n">
-        <v>150017.8513952683</v>
+        <v>150017.7487424717</v>
       </c>
       <c r="E92" s="86" t="n">
-        <v>159407.5215038081</v>
+        <v>159407.4148968833</v>
       </c>
       <c r="F92" s="86" t="n">
-        <v>171615.0662994452</v>
+        <v>171614.9554071258</v>
       </c>
       <c r="G92" s="87" t="n">
-        <v>188495.4733470173</v>
+        <v>188495.357997392</v>
       </c>
       <c r="H92" s="85" t="n">
-        <v>1217.083866173766</v>
+        <v>1217.083866163789</v>
       </c>
       <c r="I92" s="86" t="n">
         <v>972.3788727554111</v>
@@ -9554,19 +9554,19 @@
         <v>72.15937027183648</v>
       </c>
       <c r="M92" s="85" t="n">
-        <v>142329.1150689663</v>
+        <v>142329.0159554402</v>
       </c>
       <c r="N92" s="86" t="n">
-        <v>150990.2302680237</v>
+        <v>150990.1276152272</v>
       </c>
       <c r="O92" s="86" t="n">
-        <v>160118.3466929539</v>
+        <v>160118.2400860292</v>
       </c>
       <c r="P92" s="86" t="n">
-        <v>172031.9561052827</v>
+        <v>172031.8452129632</v>
       </c>
       <c r="Q92" s="87" t="n">
-        <v>188567.6327172891</v>
+        <v>188567.5173676638</v>
       </c>
       <c r="S92" s="42" t="inlineStr">
         <is>
@@ -9574,22 +9574,22 @@
         </is>
       </c>
       <c r="T92" s="85" t="n">
-        <v>119463.8186180714</v>
+        <v>119464.5368222954</v>
       </c>
       <c r="U92" s="86" t="n">
-        <v>126851.0975486954</v>
+        <v>126851.8693675706</v>
       </c>
       <c r="V92" s="86" t="n">
-        <v>134701.3361299779</v>
+        <v>134702.1618374856</v>
       </c>
       <c r="W92" s="86" t="n">
-        <v>144982.2756018889</v>
+        <v>144983.1690831112</v>
       </c>
       <c r="X92" s="87" t="n">
-        <v>159210.2982201331</v>
+        <v>159211.2861479972</v>
       </c>
       <c r="Y92" s="85" t="n">
-        <v>1024.775415644186</v>
+        <v>1024.775415636147</v>
       </c>
       <c r="Z92" s="86" t="n">
         <v>819.5886096555309</v>
@@ -9604,22 +9604,22 @@
         <v>64.76639140579327</v>
       </c>
       <c r="AD92" s="85" t="n">
-        <v>120488.5940337156</v>
+        <v>120489.3122379315</v>
       </c>
       <c r="AE92" s="86" t="n">
-        <v>127670.6861583509</v>
+        <v>127671.4579772261</v>
       </c>
       <c r="AF92" s="86" t="n">
-        <v>135301.6597119434</v>
+        <v>135302.4854194511</v>
       </c>
       <c r="AG92" s="86" t="n">
-        <v>145336.0740923478</v>
+        <v>145336.9675735701</v>
       </c>
       <c r="AH92" s="87" t="n">
-        <v>159275.0646115389</v>
+        <v>159276.052539403</v>
       </c>
       <c r="AJ92" s="126" t="n">
-        <v>35.47485969369447</v>
+        <v>35.47503193672939</v>
       </c>
       <c r="AK92" s="127" t="n">
         <v>36.47632362774299</v>
@@ -9756,22 +9756,22 @@
         </is>
       </c>
       <c r="C94" s="85" t="n">
-        <v>149696.8500097283</v>
+        <v>149696.7508962122</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>159264.6178712077</v>
+        <v>159264.5152184111</v>
       </c>
       <c r="E94" s="86" t="n">
-        <v>169449.0643680519</v>
+        <v>169448.9577611271</v>
       </c>
       <c r="F94" s="86" t="n">
-        <v>182715.3586510128</v>
+        <v>182715.2477586933</v>
       </c>
       <c r="G94" s="87" t="n">
-        <v>201023.9772333229</v>
+        <v>201023.8618836977</v>
       </c>
       <c r="H94" s="85" t="n">
-        <v>1254.296735506568</v>
+        <v>1254.296735496591</v>
       </c>
       <c r="I94" s="86" t="n">
         <v>996.0481292993957</v>
@@ -9786,19 +9786,19 @@
         <v>72.15937027183648</v>
       </c>
       <c r="M94" s="85" t="n">
-        <v>150951.1467452348</v>
+        <v>150951.0476317088</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>160260.666000507</v>
+        <v>160260.5633477105</v>
       </c>
       <c r="O94" s="86" t="n">
-        <v>170168.2283848731</v>
+        <v>170168.1217779483</v>
       </c>
       <c r="P94" s="86" t="n">
-        <v>183132.2484568503</v>
+        <v>183132.1375645308</v>
       </c>
       <c r="Q94" s="87" t="n">
-        <v>201096.1366035948</v>
+        <v>201096.0212539695</v>
       </c>
       <c r="S94" s="42" t="inlineStr">
         <is>
@@ -9806,22 +9806,22 @@
         </is>
       </c>
       <c r="T94" s="85" t="n">
-        <v>126518.6705639664</v>
+        <v>126519.3887681904</v>
       </c>
       <c r="U94" s="86" t="n">
-        <v>134449.9263572095</v>
+        <v>134450.6981760847</v>
       </c>
       <c r="V94" s="86" t="n">
-        <v>142953.2980884953</v>
+        <v>142954.123796003</v>
       </c>
       <c r="W94" s="86" t="n">
-        <v>154104.2991247606</v>
+        <v>154105.192605983</v>
       </c>
       <c r="X94" s="87" t="n">
-        <v>169506.0006699097</v>
+        <v>169506.9885977738</v>
       </c>
       <c r="Y94" s="85" t="n">
-        <v>1057.63037909861</v>
+        <v>1057.630379090571</v>
       </c>
       <c r="Z94" s="86" t="n">
         <v>840.4860188768221</v>
@@ -9836,22 +9836,22 @@
         <v>64.76639140579327</v>
       </c>
       <c r="AD94" s="85" t="n">
-        <v>127576.300943065</v>
+        <v>127577.019147281</v>
       </c>
       <c r="AE94" s="86" t="n">
-        <v>135290.4123760863</v>
+        <v>135291.1841949616</v>
       </c>
       <c r="AF94" s="86" t="n">
-        <v>143560.9839589229</v>
+        <v>143561.8096664305</v>
       </c>
       <c r="AG94" s="86" t="n">
-        <v>154458.0976152196</v>
+        <v>154458.9910964419</v>
       </c>
       <c r="AH94" s="87" t="n">
-        <v>169570.7670613155</v>
+        <v>169571.7549891796</v>
       </c>
       <c r="AJ94" s="126" t="n">
-        <v>37.51602533606992</v>
+        <v>37.51618844381618</v>
       </c>
       <c r="AK94" s="127" t="n">
         <v>38.20393949493543</v>
@@ -9988,22 +9988,22 @@
         </is>
       </c>
       <c r="C96" s="132" t="n">
-        <v>158981.1354981655</v>
+        <v>158981.0363846494</v>
       </c>
       <c r="D96" s="133" t="n">
-        <v>169734.9774373071</v>
+        <v>169734.8747845106</v>
       </c>
       <c r="E96" s="133" t="n">
-        <v>181137.8729381732</v>
+        <v>181137.7663312485</v>
       </c>
       <c r="F96" s="133" t="n">
-        <v>196111.2444344421</v>
+        <v>196111.1335421227</v>
       </c>
       <c r="G96" s="134" t="n">
-        <v>216411.7579917711</v>
+        <v>216411.6426421458</v>
       </c>
       <c r="H96" s="132" t="n">
-        <v>1262.967531876568</v>
+        <v>1262.967531866591</v>
       </c>
       <c r="I96" s="133" t="n">
         <v>1004.844413619396</v>
@@ -10018,19 +10018,19 @@
         <v>81.38165439183648</v>
       </c>
       <c r="M96" s="132" t="n">
-        <v>160244.1030300421</v>
+        <v>160244.003916516</v>
       </c>
       <c r="N96" s="133" t="n">
-        <v>170739.8218509265</v>
+        <v>170739.7191981299</v>
       </c>
       <c r="O96" s="133" t="n">
-        <v>181866.0187256345</v>
+        <v>181865.9121187098</v>
       </c>
       <c r="P96" s="133" t="n">
-        <v>196537.2353508696</v>
+        <v>196537.1244585501</v>
       </c>
       <c r="Q96" s="134" t="n">
-        <v>216493.1396461629</v>
+        <v>216493.0242965377</v>
       </c>
       <c r="S96" s="51" t="inlineStr">
         <is>
@@ -10038,22 +10038,22 @@
         </is>
       </c>
       <c r="T96" s="135" t="n">
-        <v>140996.7058523558</v>
+        <v>140997.4240565798</v>
       </c>
       <c r="U96" s="136" t="n">
-        <v>150777.5409559749</v>
+        <v>150778.3127748501</v>
       </c>
       <c r="V96" s="136" t="n">
-        <v>161180.9778779857</v>
+        <v>161181.8035854934</v>
       </c>
       <c r="W96" s="136" t="n">
-        <v>174994.0172762831</v>
+        <v>174994.9107575055</v>
       </c>
       <c r="X96" s="137" t="n">
-        <v>193501.9056976333</v>
+        <v>193502.8936254974</v>
       </c>
       <c r="Y96" s="135" t="n">
-        <v>1067.689752732331</v>
+        <v>1067.689752724293</v>
       </c>
       <c r="Z96" s="136" t="n">
         <v>850.6909766208969</v>
@@ -10068,19 +10068,19 @@
         <v>75.4655703232448</v>
       </c>
       <c r="AD96" s="135" t="n">
-        <v>142064.3956050882</v>
+        <v>142065.1138093041</v>
       </c>
       <c r="AE96" s="136" t="n">
-        <v>151628.2319325958</v>
+        <v>151629.003751471</v>
       </c>
       <c r="AF96" s="136" t="n">
-        <v>161799.0838970253</v>
+        <v>161799.909604533</v>
       </c>
       <c r="AG96" s="136" t="n">
-        <v>175358.3743668982</v>
+        <v>175359.2678481206</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>193577.3712679565</v>
+        <v>193578.3591958206</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
